--- a/Cplusplus/05. ADVANCED C++ FEATURES.xlsx
+++ b/Cplusplus/05. ADVANCED C++ FEATURES.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Document\02.Study\Programming Techniques\Cplusplus\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORK\Home\Programming-Techniques\Cplusplus\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1584" uniqueCount="1191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1653" uniqueCount="1245">
   <si>
     <t>[ ] Template specialization</t>
   </si>
@@ -2379,7 +2379,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -2395,7 +2395,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -2411,7 +2411,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -2427,7 +2427,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -2443,7 +2443,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -2459,7 +2459,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -2481,7 +2481,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -2500,7 +2500,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -2525,7 +2525,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -2550,7 +2550,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -2569,7 +2569,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -2588,7 +2588,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -2607,7 +2607,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -2635,7 +2635,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -2657,7 +2657,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -2674,7 +2674,7 @@
         <b/>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> std::enable_if_t&lt;std::is_integral_v&lt;T&gt;</t>
@@ -2683,7 +2683,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -2723,7 +2723,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -2745,7 +2745,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -2762,7 +2762,7 @@
         <b/>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <scheme val="minor"/>
       </rPr>
       <t>checkAge</t>
@@ -2771,7 +2771,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -2783,9 +2783,6 @@
     <t>=&gt; chỉ một khối được catch thực thi, phụ thuộc vào thứ tự khai báo, không phụ thuộc vào exception.</t>
   </si>
   <si>
-    <t>Tổng hợp Keywords mới trong C++ hiện đại</t>
-  </si>
-  <si>
     <t>Định nghĩa</t>
   </si>
   <si>
@@ -3107,12 +3104,6 @@
     <t>Mục đích thiết kế (C++11)</t>
   </si>
   <si>
-    <t>Ngăn implicit conversion từ conversion operators</t>
-  </si>
-  <si>
-    <t>Prevent surprising behavior</t>
-  </si>
-  <si>
     <t xml:space="preserve">    explicit operator bool() const { // C++11 extension</t>
   </si>
   <si>
@@ -3284,9 +3275,6 @@
     <t>C++17: Structured bindings ngắn gọn, type-safe</t>
   </si>
   <si>
-    <t>Cho phép define variables trong header với ODR-safe.</t>
-  </si>
-  <si>
     <t>Header-only libraries dễ hơn</t>
   </si>
   <si>
@@ -3534,1670 +3522,6 @@
   </si>
   <si>
     <t>Không dùng volatile cho synchronization</t>
-  </si>
-  <si>
-    <t>Tổng kết mức độ quan trọng trong dự án thực tế</t>
-  </si>
-  <si>
-    <t>⭐⭐⭐ Phải biết (dùng hằng ngày)</t>
-  </si>
-  <si>
-    <t>⭐⭐ Nên biết (dùng thường xuyên)</t>
-  </si>
-  <si>
-    <t>Structured bindings (C++17)</t>
-  </si>
-  <si>
-    <t>static_assert</t>
-  </si>
-  <si>
-    <t>decltype</t>
-  </si>
-  <si>
-    <t>⭐ Nâng cao (tùy domain)</t>
-  </si>
-  <si>
-    <t>Concepts (C++20) - template-heavy code</t>
-  </si>
-  <si>
-    <t>Coroutines (C++20) - async programming</t>
-  </si>
-  <si>
-    <t>Modules (C++20) - large projects</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>auto</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (C++11)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">2. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>decltype</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (C++11)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">C++98/03: Dùng </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>typeof</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (compiler extension, không chuẩn)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Kết hợp với </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>auto</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> cho generic programming</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">3. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>nullptr</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (C++11)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Literal đại diện cho null pointer, kiểu </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>std::nullptr_t</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Loại bỏ nhầm lẫn giữa </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>NULL</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (có thể là 0) và pointer</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">C++98/03: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>NULL</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> hoặc </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>0</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">4. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>constexpr</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (C++11, mở rộng C++14/17/20)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Tạo constants mạnh mẽ hơn </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>const</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">C++98/03: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>const</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>enum</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>#define</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>constexpr</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> mạnh hơn </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>const</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> vì guarantee compile-time evaluation</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">5. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>noexcept</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (C++11)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">C++98/03: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>throw()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (deprecated từ C++11, removed C++17)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>noexcept</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> hiệu quả hơn, không có runtime overhead</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">6. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>override</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> và </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>final</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (C++11)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>override</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: Chỉ rõ method ghi đè virtual function của base class</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>final</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: Ngăn class bị kế thừa hoặc method bị override</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>override</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> bắt buộc trong professional code</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">7. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>static_assert</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (C++11)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">C++98/03: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>BOOST_STATIC_ASSERT</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> hoặc compiler-specific tricks</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>static_assert</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> là chuẩn, có error message rõ ràng</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">8. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>using</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (type alias, C++11)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Alternative syntax cho type alias, mạnh hơn </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>typedef</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">C++98/03: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>typedef</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (không support template alias)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Modern C++: Luôn dùng </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>using</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">9. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>default</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> và </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>delete</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (C++11)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>default</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: Yêu cầu compiler generate default implementation</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>delete</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: Ngăn function được gọi</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">10. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>explicit</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (C++11 mở rộng)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">C++98 có </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>explicit</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> cho constructors, C++11 mở rộng cho conversion operators.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">11. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>[[attributes]]</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (C++11+)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>C++98/03: Compiler-specific (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>__attribute__</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>__declspec</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">12. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>if constexpr</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (C++17)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">C++11/14: SFINAE, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>std::enable_if</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>, template specializations</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">C++17: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>if constexpr</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> đơn giản và rõ ràng hơn nhiều</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">13. Structured Bindings </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>auto [a, b]</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (C++17)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">C++11/14: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>std::tie</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>, manual unpacking</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">14. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>inline</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> variables (C++17)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">C++11/14: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>constexpr</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> cho constants, extern cho variables</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">C++17: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>inline</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> variables đơn giản hóa header-only code</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">15. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>constinit</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (C++20)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">C++17: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>constexpr</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (nhưng constexpr yêu cầu const)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>constinit</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> cho non-const compile-time init</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">16. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>concept</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> và </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>requires</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (C++20)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">C++11/14/17: SFINAE, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>std::enable_if</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>static_assert</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">17. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>co_await</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>co_yield</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>co_return</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (C++20 Coroutines)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">18. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>consteval</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (C++20)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Function chỉ được evaluate tại compile-time (mạnh hơn </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>constexpr</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>constexpr</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: Có thể runtime hoặc compile-time</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>consteval</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: Guarantee compile-time only</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">19. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>export</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (C++20 Modules)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">C++98-17: Header files với </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>#include</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">20. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>volatile</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (cải tiến nhận thức C++20)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Dùng </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>std::atomic</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> cho thread-safe</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>auto</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>nullptr</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>override</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>final</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>constexpr</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>noexcept</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>using</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (type alias)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>default</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>delete</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>[[nodiscard]]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (C++17)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>if constexpr</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (C++17)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>inline</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> variables (C++17)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>consteval</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>constinit</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (C++20) - metaprogramming</t>
-    </r>
   </si>
   <si>
     <t>4. Modern C++ keywords</t>
@@ -5288,7 +3612,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -5304,7 +3628,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -5320,7 +3644,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -5336,7 +3660,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -5352,7 +3676,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -5381,7 +3705,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -5397,7 +3721,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -5413,7 +3737,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -5432,7 +3756,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -5448,7 +3772,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -5479,7 +3803,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -5502,7 +3826,7 @@
         <b/>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -5513,7 +3837,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -5530,7 +3854,7 @@
         <b/>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -5541,7 +3865,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -5558,7 +3882,7 @@
         <b/>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -5575,7 +3899,7 @@
         <b/>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -5592,7 +3916,7 @@
         <b/>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -5603,7 +3927,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -5622,7 +3946,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -5638,7 +3962,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -5669,7 +3993,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -5685,7 +4009,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -5704,7 +4028,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -5720,7 +4044,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -5736,7 +4060,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -5755,7 +4079,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -5774,7 +4098,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -5782,16 +4106,509 @@
       <t xml:space="preserve"> Sử dụng fully qualified names (với :: operator) để rõ ràng và tránh ambiguity.</t>
     </r>
   </si>
+  <si>
+    <t xml:space="preserve">   Phù hợp khai báo biến</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Phù hợp xác định kiểu trong khai báo tổng quát</t>
+  </si>
+  <si>
+    <t xml:space="preserve">decltype ra đời để lấy đúng kiểu của bất kỳ biểu thức/phép toán </t>
+  </si>
+  <si>
+    <t>— điều mà auto không trực tiếp làm được (cần giá trị khởi tạo với auto).</t>
+  </si>
+  <si>
+    <t>conversion operators - toán tử chuyển đổi.</t>
+  </si>
+  <si>
+    <t>Ngăn implicit conversion - chuyển đổi ngầm từ conversion operators</t>
+  </si>
+  <si>
+    <t>Prevent surprising behavior - Ngăn chặn hành vi bất ngờ .</t>
+  </si>
+  <si>
+    <t>bool b2 = static_cast&lt;bool&gt;(sp); // OK</t>
+  </si>
+  <si>
+    <t>class A {</t>
+  </si>
+  <si>
+    <t>A a1 = 5;      // Lỗi (không cho phép implicit conversion)</t>
+  </si>
+  <si>
+    <t>A a2(5);       // OK</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    explicit A(int x); // </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Chỉ cho phép khởi tạo tường minh: A a(5);</t>
+    </r>
+  </si>
+  <si>
+    <t>ODR-safe nghĩa là:</t>
+  </si>
+  <si>
+    <t>1. auto (C++11)</t>
+  </si>
+  <si>
+    <t>2. decltype (C++11)</t>
+  </si>
+  <si>
+    <t>3. nullptr (C++11)</t>
+  </si>
+  <si>
+    <t>Literal đại diện cho null pointer, kiểu std::nullptr_t.</t>
+  </si>
+  <si>
+    <t>Loại bỏ nhầm lẫn giữa NULL (có thể là 0) và pointer</t>
+  </si>
+  <si>
+    <t>C++98/03: NULL hoặc 0</t>
+  </si>
+  <si>
+    <t>C++98/03: Dùng typeof (compiler extension, không chuẩn)</t>
+  </si>
+  <si>
+    <t>Kết hợp với auto cho generic programming</t>
+  </si>
+  <si>
+    <t>4. constexpr (C++11, mở rộng C++14/17/20)</t>
+  </si>
+  <si>
+    <t>5. noexcept (C++11)</t>
+  </si>
+  <si>
+    <t>6. override và final (C++11)</t>
+  </si>
+  <si>
+    <t>override: Chỉ rõ method ghi đè virtual function của base class</t>
+  </si>
+  <si>
+    <t>final: Ngăn class bị kế thừa hoặc method bị override</t>
+  </si>
+  <si>
+    <t>Tạo constants mạnh mẽ hơn const</t>
+  </si>
+  <si>
+    <t>C++98/03: throw() (deprecated từ C++11, removed C++17)</t>
+  </si>
+  <si>
+    <t>noexcept hiệu quả hơn, không có runtime overhead</t>
+  </si>
+  <si>
+    <t>override bắt buộc trong professional code</t>
+  </si>
+  <si>
+    <t>C++98/03: const, enum, #define</t>
+  </si>
+  <si>
+    <t>constexpr mạnh hơn const vì guarantee compile-time evaluation</t>
+  </si>
+  <si>
+    <t>7. static_assert (C++11)</t>
+  </si>
+  <si>
+    <t>8. using (type alias, C++11)</t>
+  </si>
+  <si>
+    <t>9. default và delete (C++11)</t>
+  </si>
+  <si>
+    <t>Alternative syntax cho type alias, mạnh hơn typedef.</t>
+  </si>
+  <si>
+    <t>default: Yêu cầu compiler generate default implementation</t>
+  </si>
+  <si>
+    <t>delete: Ngăn function được gọi</t>
+  </si>
+  <si>
+    <t>C++98/03: typedef (không support template alias)</t>
+  </si>
+  <si>
+    <t>Modern C++: Luôn dùng using</t>
+  </si>
+  <si>
+    <t>C++98/03: BOOST_STATIC_ASSERT hoặc compiler-specific tricks</t>
+  </si>
+  <si>
+    <t>static_assert là chuẩn, có error message rõ ràng</t>
+  </si>
+  <si>
+    <t>10. explicit (C++11 mở rộng)</t>
+  </si>
+  <si>
+    <t>11. [[attributes]] (C++11+)</t>
+  </si>
+  <si>
+    <t>12. if constexpr (C++17)</t>
+  </si>
+  <si>
+    <t>C++98 có explicit cho constructors, C++11 mở rộng cho conversion operators.</t>
+  </si>
+  <si>
+    <t>C++11/14: SFINAE, std::enable_if, template specializations</t>
+  </si>
+  <si>
+    <t>C++17: if constexpr đơn giản và rõ ràng hơn nhiều</t>
+  </si>
+  <si>
+    <t>C++98/03: Compiler-specific (__attribute__, __declspec)</t>
+  </si>
+  <si>
+    <t>13. Structured Bindings auto [a, b] (C++17)</t>
+  </si>
+  <si>
+    <t>14. inline variables (C++17)</t>
+  </si>
+  <si>
+    <t>C++17: constexpr (nhưng constexpr yêu cầu const)</t>
+  </si>
+  <si>
+    <t>constinit cho non-const compile-time init</t>
+  </si>
+  <si>
+    <t>C++11/14: constexpr cho constants, extern cho variables</t>
+  </si>
+  <si>
+    <t>C++17: inline variables đơn giản hóa header-only code</t>
+  </si>
+  <si>
+    <t>C++11/14: std::tie, manual unpacking</t>
+  </si>
+  <si>
+    <t>Function chỉ được evaluate tại compile-time (mạnh hơn constexpr).</t>
+  </si>
+  <si>
+    <t>constexpr: Có thể runtime hoặc compile-time</t>
+  </si>
+  <si>
+    <t>consteval: Guarantee compile-time only</t>
+  </si>
+  <si>
+    <t>C++11/14/17: SFINAE, std::enable_if, static_assert</t>
+  </si>
+  <si>
+    <t>Dùng std::atomic cho thread-safe</t>
+  </si>
+  <si>
+    <t>C++98-17: Header files với #include</t>
+  </si>
+  <si>
+    <t>"inline" không có nghĩa là "inline code", mà là "multiple definitions allowed"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15. extern </t>
+  </si>
+  <si>
+    <t>Báo với compiler: "biến này tồn tại ở đâu đó, sẽ được resolve lúc linking"</t>
+  </si>
+  <si>
+    <t>Không allocate memory tại điểm khai báo</t>
+  </si>
+  <si>
+    <r>
+      <t>Declaration</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> mà không phải </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>definition</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">extern int counter; // Declaration only </t>
+  </si>
+  <si>
+    <t xml:space="preserve">extern const int MAX_SIZE; // Declaration const </t>
+  </si>
+  <si>
+    <t xml:space="preserve">// ===== config.cpp ===== (BẮT BUỘC) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">int counter = 0; // Definition (allocate memory) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">const int MAX_SIZE = 100; // Definition </t>
+  </si>
+  <si>
+    <t xml:space="preserve">// ===== main.cpp ===== </t>
+  </si>
+  <si>
+    <t xml:space="preserve">#include "config.h" </t>
+  </si>
+  <si>
+    <t>counter++; // OK, trỏ đến definition trong config.cpp</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">// ===== config.h ===== </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA626A4"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <t>16. constinit (C++20)</t>
+  </si>
+  <si>
+    <t>17. concept và requires (C++20)</t>
+  </si>
+  <si>
+    <t>18. co_await, co_yield, co_return (C++20 Coroutines)</t>
+  </si>
+  <si>
+    <t>19. consteval (C++20)</t>
+  </si>
+  <si>
+    <t>20. export (C++20 Modules)</t>
+  </si>
+  <si>
+    <t>21. volatile (cải tiến nhận thức C++20)</t>
+  </si>
+  <si>
+    <t>int value = 10;  // ❌ KHÔNG có extern</t>
+  </si>
+  <si>
+    <t>// a.cpp</t>
+  </si>
+  <si>
+    <t>#include "header.h"  // Define value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">// b.cpp  </t>
+  </si>
+  <si>
+    <t>#include "header.h"  // Define value lần 2</t>
+  </si>
+  <si>
+    <t>// ❌ Linker error: multiple definition of 'value'</t>
+  </si>
+  <si>
+    <t>Với extern - CẦN include</t>
+  </si>
+  <si>
+    <t>// ===== main.cpp =====</t>
+  </si>
+  <si>
+    <t>// ===== bad.cpp =====</t>
+  </si>
+  <si>
+    <t>// KHÔNG include config.h</t>
+  </si>
+  <si>
+    <t>int x = value;  // ❌ Compiler error: 'value' was not declared</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                // Compiler không biết 'value' là gì</t>
+  </si>
+  <si>
+    <t>Có thể không include nhưng KHÔNG nên:</t>
+  </si>
+  <si>
+    <t>// bad.cpp</t>
+  </si>
+  <si>
+    <t>extern int value;  // Manual declaration (trùng với header)</t>
+  </si>
+  <si>
+    <t>int x = value;     // OK nhưng bad practice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                   // - Dễ type mismatch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                   // - Duplicate code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                   // - Maintainability thấp</t>
+  </si>
+  <si>
+    <t>extern với biến</t>
+  </si>
+  <si>
+    <t>extern với hàm</t>
+  </si>
+  <si>
+    <t>// ===== header.h =====</t>
+  </si>
+  <si>
+    <t>int add(int a, int b);  // ✅ Không cần extern (tự động có)</t>
+  </si>
+  <si>
+    <t>// Tương đương: extern int add(int a, int b);</t>
+  </si>
+  <si>
+    <t>// ===== source.cpp =====</t>
+  </si>
+  <si>
+    <t>int add(int a, int b) {  // Definition</t>
+  </si>
+  <si>
+    <t>#include "header.h"</t>
+  </si>
+  <si>
+    <t>int x = add(1, 2);      // OK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn có thể define biến trong header, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   include ở nhiều tệp mà không vi phạm quy tắc một định nghĩa của C++.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Giúp chia sẻ giá trị biến toàn cục hoặc static member </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   xuyên suốt project mà không bị lỗi khi liên kết.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Trường hợp ĐẶC BIỆT phải dùng extern với hàm</t>
+  </si>
+  <si>
+    <t>// ===== api.h =====</t>
+  </si>
+  <si>
+    <t>#ifdef __cplusplus</t>
+  </si>
+  <si>
+    <t>extern "C" {  // ✅ Đây là extern KHÁC (không phải external linkage)</t>
+  </si>
+  <si>
+    <t>void c_compatible_function(int x);</t>
+  </si>
+  <si>
+    <t>int another_c_function();</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Cho phép </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>define</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> biến trong header</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Compiler đảm bảo chỉ có </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1 instance duy nhất</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> qua tất cả translation units</t>
+    </r>
+  </si>
+  <si>
+    <t>extern "C" - C linkage</t>
+  </si>
+  <si>
+    <t>Explicit extern (rất hiếm)</t>
+  </si>
+  <si>
+    <t>// ===== weird.cpp =====</t>
+  </si>
+  <si>
+    <t>// Muốn document rõ ràng: hàm này có external linkage</t>
+  </si>
+  <si>
+    <t>void documentedFunction() {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Implementation</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">extern void documentedFunction();  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>// ⚠️ Hợp lệ nhưng thừa</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">=&gt; dùng khi không thể include header </t>
+  </si>
+  <si>
+    <t>vì không có đường dẫn trực tiếp.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="163"/>
       <scheme val="minor"/>
@@ -5813,7 +4630,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="163"/>
       <scheme val="minor"/>
@@ -5821,7 +4638,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Arial"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="163"/>
       <scheme val="minor"/>
@@ -5830,7 +4647,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Arial"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="163"/>
       <scheme val="minor"/>
@@ -5839,29 +4656,15 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Arial"/>
+      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="163"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial Unicode MS"/>
     </font>
     <font>
       <sz val="11"/>
@@ -5880,7 +4683,27 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF00B0F0"/>
-      <name val="Arial"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="163"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFA626A4"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="163"/>
       <scheme val="minor"/>
@@ -5954,7 +4777,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -6016,13 +4839,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -6036,10 +4856,39 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6448,8 +5297,8 @@
       <c r="AD2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="AQ2" s="31" t="s">
-        <v>1121</v>
+      <c r="AQ2" s="30" t="s">
+        <v>1044</v>
       </c>
     </row>
     <row r="3" spans="1:57" ht="15">
@@ -6463,10 +5312,10 @@
         <v>31</v>
       </c>
       <c r="AQ3" s="13" t="s">
-        <v>1122</v>
+        <v>1045</v>
       </c>
       <c r="BE3" s="13" t="s">
-        <v>1133</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="4" spans="1:57">
@@ -6479,11 +5328,11 @@
       <c r="AD4" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="AQ4" s="30" t="s">
-        <v>1123</v>
-      </c>
-      <c r="BE4" s="30" t="s">
-        <v>1151</v>
+      <c r="AQ4" s="29" t="s">
+        <v>1046</v>
+      </c>
+      <c r="BE4" s="29" t="s">
+        <v>1074</v>
       </c>
     </row>
     <row r="5" spans="1:57">
@@ -6496,11 +5345,11 @@
       <c r="AD5" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="AQ5" s="30" t="s">
-        <v>1124</v>
-      </c>
-      <c r="BE5" s="30" t="s">
-        <v>1134</v>
+      <c r="AQ5" s="29" t="s">
+        <v>1047</v>
+      </c>
+      <c r="BE5" s="29" t="s">
+        <v>1057</v>
       </c>
     </row>
     <row r="6" spans="1:57">
@@ -6513,8 +5362,8 @@
       <c r="AD6" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="AQ6" s="30" t="s">
-        <v>1125</v>
+      <c r="AQ6" s="29" t="s">
+        <v>1048</v>
       </c>
     </row>
     <row r="7" spans="1:57" ht="15">
@@ -6527,22 +5376,22 @@
       <c r="AD7" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="AQ7" s="30" t="s">
-        <v>1126</v>
+      <c r="AQ7" s="29" t="s">
+        <v>1049</v>
       </c>
       <c r="BE7" s="13" t="s">
-        <v>1135</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="8" spans="1:57">
       <c r="A8" s="3"/>
       <c r="Q8" s="3"/>
       <c r="AD8" s="3"/>
-      <c r="AQ8" s="30" t="s">
-        <v>1127</v>
-      </c>
-      <c r="BE8" s="30" t="s">
-        <v>1136</v>
+      <c r="AQ8" s="29" t="s">
+        <v>1050</v>
+      </c>
+      <c r="BE8" s="29" t="s">
+        <v>1059</v>
       </c>
     </row>
     <row r="9" spans="1:57" ht="15">
@@ -6555,11 +5404,11 @@
       <c r="AD9" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="AQ9" s="30" t="s">
-        <v>1128</v>
-      </c>
-      <c r="BE9" s="30" t="s">
-        <v>1152</v>
+      <c r="AQ9" s="29" t="s">
+        <v>1051</v>
+      </c>
+      <c r="BE9" s="29" t="s">
+        <v>1075</v>
       </c>
     </row>
     <row r="10" spans="1:57">
@@ -6572,11 +5421,11 @@
       <c r="AD10" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="AQ10" s="30" t="s">
-        <v>1129</v>
+      <c r="AQ10" s="29" t="s">
+        <v>1052</v>
       </c>
       <c r="BE10" s="11" t="s">
-        <v>1153</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="11" spans="1:57">
@@ -6589,11 +5438,11 @@
       <c r="AD11" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="AQ11" s="30" t="s">
-        <v>1130</v>
-      </c>
-      <c r="BE11" s="30" t="s">
-        <v>1137</v>
+      <c r="AQ11" s="29" t="s">
+        <v>1053</v>
+      </c>
+      <c r="BE11" s="29" t="s">
+        <v>1060</v>
       </c>
     </row>
     <row r="12" spans="1:57">
@@ -6606,11 +5455,11 @@
       <c r="AD12" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="AQ12" s="30" t="s">
-        <v>1148</v>
-      </c>
-      <c r="BE12" s="30" t="s">
-        <v>1138</v>
+      <c r="AQ12" s="29" t="s">
+        <v>1071</v>
+      </c>
+      <c r="BE12" s="29" t="s">
+        <v>1061</v>
       </c>
     </row>
     <row r="13" spans="1:57">
@@ -6620,47 +5469,47 @@
       <c r="Q13" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="AQ13" s="30" t="s">
-        <v>1131</v>
-      </c>
-      <c r="BE13" s="30" t="s">
-        <v>1139</v>
+      <c r="AQ13" s="29" t="s">
+        <v>1054</v>
+      </c>
+      <c r="BE13" s="29" t="s">
+        <v>1062</v>
       </c>
     </row>
     <row r="14" spans="1:57">
       <c r="A14" s="3"/>
-      <c r="AQ14" s="30" t="s">
-        <v>1132</v>
+      <c r="AQ14" s="29" t="s">
+        <v>1055</v>
       </c>
     </row>
     <row r="15" spans="1:57" ht="15">
       <c r="A15" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="AQ15" s="30" t="s">
-        <v>1149</v>
+      <c r="AQ15" s="29" t="s">
+        <v>1072</v>
       </c>
       <c r="BE15" s="13" t="s">
-        <v>1140</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="16" spans="1:57">
       <c r="A16" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="AQ16" s="30" t="s">
-        <v>1150</v>
-      </c>
-      <c r="BE16" s="30" t="s">
-        <v>1141</v>
+      <c r="AQ16" s="29" t="s">
+        <v>1073</v>
+      </c>
+      <c r="BE16" s="29" t="s">
+        <v>1064</v>
       </c>
     </row>
     <row r="17" spans="1:57">
       <c r="A17" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="BE17" s="30" t="s">
-        <v>1142</v>
+      <c r="BE17" s="29" t="s">
+        <v>1065</v>
       </c>
     </row>
     <row r="18" spans="1:57">
@@ -6668,43 +5517,43 @@
         <v>11</v>
       </c>
       <c r="AQ18" s="9"/>
-      <c r="BE18" s="30" t="s">
-        <v>1143</v>
+      <c r="BE18" s="29" t="s">
+        <v>1066</v>
       </c>
     </row>
     <row r="19" spans="1:57">
       <c r="A19" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="BE19" s="30" t="s">
-        <v>1144</v>
+      <c r="BE19" s="29" t="s">
+        <v>1067</v>
       </c>
     </row>
     <row r="20" spans="1:57">
       <c r="AQ20" s="11"/>
-      <c r="BE20" s="30" t="s">
-        <v>1145</v>
+      <c r="BE20" s="29" t="s">
+        <v>1068</v>
       </c>
     </row>
     <row r="21" spans="1:57">
-      <c r="BE21" s="30" t="s">
-        <v>1146</v>
+      <c r="BE21" s="29" t="s">
+        <v>1069</v>
       </c>
     </row>
     <row r="22" spans="1:57">
-      <c r="BE22" s="30" t="s">
-        <v>1147</v>
+      <c r="BE22" s="29" t="s">
+        <v>1070</v>
       </c>
     </row>
     <row r="23" spans="1:57">
       <c r="AQ23" s="9"/>
-      <c r="BE23" s="30" t="s">
-        <v>1154</v>
+      <c r="BE23" s="29" t="s">
+        <v>1077</v>
       </c>
     </row>
     <row r="24" spans="1:57">
-      <c r="BE24" s="30" t="s">
-        <v>1155</v>
+      <c r="BE24" s="29" t="s">
+        <v>1078</v>
       </c>
     </row>
     <row r="31" spans="1:57">
@@ -9027,8 +7876,8 @@
       </c>
     </row>
     <row r="21" spans="1:42" s="9" customFormat="1" ht="15" customHeight="1">
-      <c r="A21" s="33" t="s">
-        <v>1161</v>
+      <c r="A21" s="32" t="s">
+        <v>1084</v>
       </c>
       <c r="U21" s="15" t="s">
         <v>795</v>
@@ -9107,8 +7956,8 @@
       <c r="A29" s="10" t="s">
         <v>354</v>
       </c>
-      <c r="U29" s="37" t="s">
-        <v>1176</v>
+      <c r="U29" s="36" t="s">
+        <v>1099</v>
       </c>
       <c r="V29" s="14"/>
       <c r="W29" s="14"/>
@@ -9129,7 +7978,7 @@
       </c>
       <c r="U31" s="14"/>
       <c r="V31" s="21" t="s">
-        <v>1177</v>
+        <v>1100</v>
       </c>
       <c r="W31" s="14"/>
     </row>
@@ -9164,7 +8013,7 @@
       <c r="W34" s="14"/>
     </row>
     <row r="35" spans="1:29" s="9" customFormat="1" ht="15" customHeight="1">
-      <c r="U35" s="38" t="s">
+      <c r="U35" s="37" t="s">
         <v>44</v>
       </c>
       <c r="V35" s="14"/>
@@ -9179,21 +8028,21 @@
       <c r="A37" s="16" t="s">
         <v>399</v>
       </c>
-      <c r="AC37" s="32" t="s">
+      <c r="AC37" s="31" t="s">
         <v>433</v>
       </c>
     </row>
     <row r="38" spans="1:29" s="9" customFormat="1" ht="15" customHeight="1">
       <c r="A38" s="14" t="s">
-        <v>1156</v>
+        <v>1079</v>
       </c>
       <c r="AC38" s="14" t="s">
-        <v>1158</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="39" spans="1:29" s="9" customFormat="1" ht="15" customHeight="1">
       <c r="A39" s="18" t="s">
-        <v>1157</v>
+        <v>1080</v>
       </c>
       <c r="AC39" s="7" t="s">
         <v>434</v>
@@ -9345,7 +8194,7 @@
       <c r="A59" s="10" t="s">
         <v>412</v>
       </c>
-      <c r="AC59" s="34" t="s">
+      <c r="AC59" s="33" t="s">
         <v>450</v>
       </c>
       <c r="AD59" s="14"/>
@@ -9354,8 +8203,8 @@
       <c r="A60" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="AC60" s="34" t="s">
-        <v>1167</v>
+      <c r="AC60" s="33" t="s">
+        <v>1090</v>
       </c>
       <c r="AD60" s="14"/>
     </row>
@@ -9419,7 +8268,7 @@
         <v>417</v>
       </c>
       <c r="AC69" s="27" t="s">
-        <v>1168</v>
+        <v>1091</v>
       </c>
       <c r="AD69" s="18"/>
     </row>
@@ -9428,7 +8277,7 @@
         <v>418</v>
       </c>
       <c r="AC70" s="27" t="s">
-        <v>1169</v>
+        <v>1092</v>
       </c>
       <c r="AD70" s="18"/>
     </row>
@@ -9437,14 +8286,14 @@
         <v>44</v>
       </c>
       <c r="AC71" s="27" t="s">
-        <v>1170</v>
+        <v>1093</v>
       </c>
       <c r="AD71" s="18"/>
     </row>
     <row r="72" spans="1:30" s="9" customFormat="1" ht="15" customHeight="1">
       <c r="A72" s="10"/>
       <c r="AC72" s="27" t="s">
-        <v>1171</v>
+        <v>1094</v>
       </c>
       <c r="AD72" s="18"/>
     </row>
@@ -9453,7 +8302,7 @@
         <v>419</v>
       </c>
       <c r="AC73" s="27" t="s">
-        <v>1172</v>
+        <v>1095</v>
       </c>
       <c r="AD73" s="18"/>
     </row>
@@ -9494,12 +8343,12 @@
     </row>
     <row r="81" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1">
       <c r="A81" s="14" t="s">
-        <v>1159</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="82" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1">
       <c r="A82" s="15" t="s">
-        <v>1160</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="83" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1"/>
@@ -9525,7 +8374,7 @@
     </row>
     <row r="88" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1">
       <c r="A88" s="21" t="s">
-        <v>1162</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="89" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1">
@@ -9558,7 +8407,7 @@
       <c r="A95" s="16" t="s">
         <v>456</v>
       </c>
-      <c r="Z95" s="32" t="s">
+      <c r="Z95" s="31" t="s">
         <v>481</v>
       </c>
     </row>
@@ -9577,7 +8426,7 @@
         <v>318</v>
       </c>
       <c r="AA96" s="18"/>
-      <c r="AS96" s="36" t="s">
+      <c r="AS96" s="35" t="s">
         <v>491</v>
       </c>
       <c r="AT96" s="20"/>
@@ -9587,10 +8436,10 @@
     </row>
     <row r="97" spans="1:60" s="9" customFormat="1" ht="15" customHeight="1">
       <c r="A97" s="14" t="s">
-        <v>1173</v>
-      </c>
-      <c r="Z97" s="35" t="s">
-        <v>1174</v>
+        <v>1096</v>
+      </c>
+      <c r="Z97" s="34" t="s">
+        <v>1097</v>
       </c>
       <c r="AA97" s="18"/>
       <c r="AS97" s="21" t="s">
@@ -9600,10 +8449,10 @@
     </row>
     <row r="98" spans="1:60" s="9" customFormat="1" ht="15" customHeight="1">
       <c r="A98" s="14" t="s">
-        <v>1163</v>
-      </c>
-      <c r="Z98" s="35" t="s">
-        <v>1175</v>
+        <v>1086</v>
+      </c>
+      <c r="Z98" s="34" t="s">
+        <v>1098</v>
       </c>
       <c r="AA98" s="18"/>
       <c r="AS98" s="15" t="s">
@@ -9957,24 +8806,24 @@
       <c r="A127" s="16" t="s">
         <v>504</v>
       </c>
-      <c r="Z127" s="32" t="s">
+      <c r="Z127" s="31" t="s">
         <v>534</v>
       </c>
     </row>
     <row r="128" spans="1:48" s="9" customFormat="1" ht="15" customHeight="1">
       <c r="A128" s="14" t="s">
-        <v>1165</v>
+        <v>1088</v>
       </c>
       <c r="Z128" s="14" t="s">
-        <v>1178</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="129" spans="1:26" s="9" customFormat="1" ht="15" customHeight="1">
       <c r="A129" s="18" t="s">
-        <v>1164</v>
+        <v>1087</v>
       </c>
       <c r="Z129" s="14" t="s">
-        <v>1166</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="130" spans="1:26" s="9" customFormat="1" ht="15" customHeight="1">
@@ -10423,7 +9272,7 @@
       <c r="E2" s="20"/>
       <c r="F2" s="20"/>
       <c r="G2" s="20"/>
-      <c r="V2" s="36" t="s">
+      <c r="V2" s="35" t="s">
         <v>572</v>
       </c>
       <c r="W2" s="20"/>
@@ -10432,7 +9281,7 @@
       <c r="Z2" s="20"/>
       <c r="AA2" s="20"/>
       <c r="AB2" s="20"/>
-      <c r="AJ2" s="36" t="s">
+      <c r="AJ2" s="35" t="s">
         <v>585</v>
       </c>
       <c r="AK2" s="20"/>
@@ -10449,7 +9298,7 @@
     </row>
     <row r="3" spans="1:47" s="9" customFormat="1" ht="15" customHeight="1">
       <c r="A3" s="14" t="s">
-        <v>1180</v>
+        <v>1103</v>
       </c>
       <c r="V3" s="10" t="s">
         <v>573</v>
@@ -10460,7 +9309,7 @@
     </row>
     <row r="4" spans="1:47" s="9" customFormat="1" ht="15" customHeight="1">
       <c r="A4" s="14" t="s">
-        <v>1179</v>
+        <v>1102</v>
       </c>
       <c r="V4" s="10" t="s">
         <v>574</v>
@@ -10668,13 +9517,13 @@
       </c>
     </row>
     <row r="25" spans="1:63" s="9" customFormat="1" ht="15" customHeight="1">
-      <c r="A25" s="35" t="s">
-        <v>1181</v>
+      <c r="A25" s="34" t="s">
+        <v>1104</v>
       </c>
     </row>
     <row r="26" spans="1:63" s="9" customFormat="1" ht="15" customHeight="1">
-      <c r="A26" s="35" t="s">
-        <v>1182</v>
+      <c r="A26" s="34" t="s">
+        <v>1105</v>
       </c>
     </row>
     <row r="27" spans="1:63" s="9" customFormat="1" ht="15" customHeight="1"/>
@@ -10818,12 +9667,12 @@
     </row>
     <row r="38" spans="1:72" s="9" customFormat="1" ht="15" customHeight="1">
       <c r="A38" s="14" t="s">
-        <v>1184</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="39" spans="1:72" s="9" customFormat="1" ht="15" customHeight="1">
       <c r="A39" s="18" t="s">
-        <v>1183</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="40" spans="1:72" s="9" customFormat="1" ht="15" customHeight="1">
@@ -10959,7 +9808,7 @@
     </row>
     <row r="59" spans="1:25" s="9" customFormat="1" ht="15" customHeight="1">
       <c r="A59" s="14" t="s">
-        <v>1185</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="60" spans="1:25" s="9" customFormat="1" ht="15" customHeight="1"/>
@@ -11109,7 +9958,7 @@
     </row>
     <row r="93" spans="1:26" s="9" customFormat="1" ht="15" customHeight="1">
       <c r="A93" s="14" t="s">
-        <v>1186</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="94" spans="1:26" s="9" customFormat="1" ht="15" customHeight="1"/>
@@ -11222,16 +10071,16 @@
     </row>
     <row r="110" spans="1:37" s="9" customFormat="1" ht="15" customHeight="1">
       <c r="A110" s="14" t="s">
-        <v>1188</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="111" spans="1:37" s="9" customFormat="1" ht="15" customHeight="1">
       <c r="A111" s="14" t="s">
-        <v>1189</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="112" spans="1:37" s="9" customFormat="1" ht="15" customHeight="1">
-      <c r="A112" s="36" t="s">
+      <c r="A112" s="35" t="s">
         <v>687</v>
       </c>
       <c r="B112" s="20"/>
@@ -11344,7 +10193,7 @@
       </c>
     </row>
     <row r="123" spans="1:37" s="9" customFormat="1" ht="15" customHeight="1">
-      <c r="A123" s="36" t="s">
+      <c r="A123" s="35" t="s">
         <v>693</v>
       </c>
       <c r="B123" s="20"/>
@@ -11387,7 +10236,7 @@
     </row>
     <row r="128" spans="1:37" s="9" customFormat="1" ht="15" customHeight="1">
       <c r="A128" s="15" t="s">
-        <v>1187</v>
+        <v>1110</v>
       </c>
       <c r="B128" s="18"/>
       <c r="C128" s="18"/>
@@ -11440,7 +10289,7 @@
     </row>
     <row r="135" spans="1:22" s="9" customFormat="1" ht="15" customHeight="1">
       <c r="A135" s="14" t="s">
-        <v>1190</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="136" spans="1:22" s="9" customFormat="1" ht="15" customHeight="1">
@@ -11449,7 +10298,7 @@
       </c>
       <c r="B136" s="18"/>
       <c r="C136" s="18"/>
-      <c r="R136" s="36" t="s">
+      <c r="R136" s="35" t="s">
         <v>455</v>
       </c>
       <c r="S136" s="20"/>
@@ -11765,2509 +10614,2171 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A712"/>
+  <dimension ref="A1:BL287"/>
   <sheetFormatPr defaultColWidth="3" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="16384" width="3" style="9"/>
+    <col min="1" max="16384" width="3" style="43"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="15">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:53" s="40" customFormat="1" ht="15.75" thickBot="1">
+      <c r="A1" s="39" t="s">
+        <v>1127</v>
+      </c>
+      <c r="AC1" s="41" t="s">
+        <v>1128</v>
+      </c>
+      <c r="BA1" s="41" t="s">
+        <v>1129</v>
+      </c>
+    </row>
+    <row r="2" spans="1:53" ht="15">
+      <c r="A2" s="42" t="s">
         <v>797</v>
       </c>
-    </row>
-    <row r="3" spans="1:1" ht="15">
-      <c r="A3" s="13" t="s">
-        <v>1058</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" ht="15">
-      <c r="A5" s="13" t="s">
+      <c r="AC2" s="42" t="s">
+        <v>797</v>
+      </c>
+      <c r="BA2" s="42" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="3" spans="1:53" ht="15">
+      <c r="A3" s="25" t="s">
         <v>798</v>
       </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" s="9" t="s">
+      <c r="AC3" s="25" t="s">
+        <v>812</v>
+      </c>
+      <c r="BA3" s="44" t="s">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="4" spans="1:53" ht="15">
+      <c r="A4" s="42" t="s">
         <v>799</v>
       </c>
-    </row>
-    <row r="9" spans="1:1" ht="15">
-      <c r="A9" s="13" t="s">
+      <c r="AC4" s="42" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="5" spans="1:53" ht="15">
+      <c r="A5" s="45" t="s">
         <v>800</v>
       </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" s="11"/>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" s="11" t="s">
+      <c r="AC5" s="45" t="s">
+        <v>813</v>
+      </c>
+      <c r="BA5" s="42" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="6" spans="1:53">
+      <c r="A6" s="45" t="s">
         <v>801</v>
       </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" s="11" t="s">
+      <c r="AC6" s="45" t="s">
+        <v>814</v>
+      </c>
+      <c r="BA6" s="45" t="s">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="7" spans="1:53" ht="15">
+      <c r="A7" s="25" t="s">
+        <v>1114</v>
+      </c>
+      <c r="AC7" s="25" t="s">
+        <v>1115</v>
+      </c>
+      <c r="BA7" s="45" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="8" spans="1:53" ht="15">
+      <c r="A8" s="42" t="s">
         <v>802</v>
       </c>
-    </row>
-    <row r="14" spans="1:1" ht="15">
-      <c r="A14" s="13" t="s">
+      <c r="AC8" s="42" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="9" spans="1:53" ht="15">
+      <c r="A9" s="46" t="s">
         <v>803</v>
       </c>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" s="29" t="s">
+      <c r="AC9" s="46" t="s">
+        <v>815</v>
+      </c>
+      <c r="BA9" s="42" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="10" spans="1:53" ht="15">
+      <c r="A10" s="23" t="s">
         <v>804</v>
       </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" s="29" t="s">
+      <c r="AC10" s="46" t="s">
+        <v>816</v>
+      </c>
+      <c r="BA10" s="46" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="11" spans="1:53">
+      <c r="A11" s="46"/>
+      <c r="AC11" s="46" t="s">
+        <v>817</v>
+      </c>
+      <c r="BA11" s="46"/>
+    </row>
+    <row r="12" spans="1:53">
+      <c r="A12" s="46" t="s">
         <v>805</v>
       </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" s="10"/>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" s="29" t="s">
+      <c r="AC12" s="46"/>
+      <c r="BA12" s="46" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="13" spans="1:53" ht="15">
+      <c r="A13" s="46" t="s">
         <v>806</v>
       </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" s="29" t="s">
+      <c r="AC13" s="23" t="s">
+        <v>818</v>
+      </c>
+      <c r="BA13" s="46" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="14" spans="1:53">
+      <c r="A14" s="46"/>
+      <c r="AC14" s="46" t="s">
+        <v>819</v>
+      </c>
+      <c r="BA14" s="46" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="15" spans="1:53">
+      <c r="A15" s="46" t="s">
         <v>807</v>
       </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="10"/>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22" s="29" t="s">
+      <c r="AC15" s="46" t="s">
+        <v>820</v>
+      </c>
+      <c r="BA15" s="46" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="16" spans="1:53">
+      <c r="A16" s="46" t="s">
         <v>808</v>
       </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" s="29" t="s">
+      <c r="AC16" s="46" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="17" spans="1:53" ht="15">
+      <c r="AC17" s="46" t="s">
+        <v>44</v>
+      </c>
+      <c r="BA17" s="42" t="s">
         <v>809</v>
       </c>
     </row>
-    <row r="25" spans="1:1" ht="15">
-      <c r="A25" s="13" t="s">
+    <row r="18" spans="1:53" ht="15">
+      <c r="A18" s="42" t="s">
+        <v>809</v>
+      </c>
+      <c r="BA18" s="45" t="s">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="19" spans="1:53" ht="15">
+      <c r="A19" s="45" t="s">
         <v>810</v>
       </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" s="11"/>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" s="11" t="s">
+      <c r="AC19" s="42" t="s">
+        <v>809</v>
+      </c>
+      <c r="BA19" s="45" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="20" spans="1:53">
+      <c r="A20" s="45" t="s">
         <v>811</v>
       </c>
-    </row>
-    <row r="28" spans="1:1">
-      <c r="A28" s="11" t="s">
-        <v>812</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" ht="15">
-      <c r="A32" s="13" t="s">
-        <v>1059</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" ht="15">
-      <c r="A34" s="13" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1">
-      <c r="A36" s="9" t="s">
-        <v>813</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" ht="15">
-      <c r="A38" s="13" t="s">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1">
-      <c r="A39" s="11"/>
-    </row>
-    <row r="40" spans="1:1">
-      <c r="A40" s="11" t="s">
-        <v>814</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" s="11" t="s">
-        <v>815</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" ht="15">
-      <c r="A43" s="13" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" s="29" t="s">
-        <v>816</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1">
-      <c r="A46" s="29" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1">
-      <c r="A47" s="29" t="s">
-        <v>818</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1">
-      <c r="A48" s="10"/>
-    </row>
-    <row r="49" spans="1:1">
-      <c r="A49" s="29" t="s">
-        <v>819</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1">
-      <c r="A50" s="29" t="s">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1">
-      <c r="A51" s="29" t="s">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1">
-      <c r="A52" s="29" t="s">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1">
-      <c r="A53" s="29" t="s">
+      <c r="AC20" s="45" t="s">
+        <v>1133</v>
+      </c>
+    </row>
+    <row r="21" spans="1:53">
+      <c r="AC21" s="45" t="s">
+        <v>1134</v>
+      </c>
+    </row>
+    <row r="22" spans="1:53" ht="15">
+      <c r="AC22" s="25" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="23" spans="1:53" ht="15">
+      <c r="AC23" s="38" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="24" spans="1:53" ht="15" thickBot="1"/>
+    <row r="25" spans="1:53" s="40" customFormat="1" ht="15.75" thickBot="1">
+      <c r="A25" s="39" t="s">
+        <v>1135</v>
+      </c>
+      <c r="Z25" s="41" t="s">
+        <v>1136</v>
+      </c>
+      <c r="AU25" s="41" t="s">
+        <v>1137</v>
+      </c>
+    </row>
+    <row r="26" spans="1:53" ht="15">
+      <c r="A26" s="42" t="s">
+        <v>797</v>
+      </c>
+      <c r="Z26" s="23" t="s">
+        <v>797</v>
+      </c>
+      <c r="AU26" s="42" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="27" spans="1:53" ht="15">
+      <c r="A27" s="25" t="s">
+        <v>829</v>
+      </c>
+      <c r="Z27" s="44" t="s">
+        <v>844</v>
+      </c>
+      <c r="AU27" s="45" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="28" spans="1:53">
+      <c r="AU28" s="45" t="s">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="29" spans="1:53" ht="15">
+      <c r="A29" s="42" t="s">
+        <v>799</v>
+      </c>
+      <c r="Z29" s="42" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="30" spans="1:53" ht="15">
+      <c r="A30" s="45" t="s">
+        <v>830</v>
+      </c>
+      <c r="Z30" s="45" t="s">
+        <v>845</v>
+      </c>
+      <c r="AU30" s="42" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="31" spans="1:53">
+      <c r="A31" s="45" t="s">
+        <v>1140</v>
+      </c>
+      <c r="Z31" s="45" t="s">
+        <v>846</v>
+      </c>
+      <c r="AU31" s="45" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="32" spans="1:53">
+      <c r="A32" s="45" t="s">
+        <v>831</v>
+      </c>
+      <c r="Z32" s="45" t="s">
+        <v>847</v>
+      </c>
+      <c r="AU32" s="45" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="33" spans="1:47">
+      <c r="AU33" s="45" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="34" spans="1:47" ht="15">
+      <c r="A34" s="42" t="s">
+        <v>802</v>
+      </c>
+      <c r="Z34" s="42" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="35" spans="1:47" ht="15">
+      <c r="A35" s="47" t="s">
+        <v>832</v>
+      </c>
+      <c r="Z35" s="46" t="s">
+        <v>848</v>
+      </c>
+      <c r="AU35" s="42" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="36" spans="1:47">
+      <c r="A36" s="47" t="s">
+        <v>833</v>
+      </c>
+      <c r="Z36" s="46" t="s">
+        <v>543</v>
+      </c>
+      <c r="AU36" s="46" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="37" spans="1:47">
+      <c r="A37" s="47" t="s">
+        <v>834</v>
+      </c>
+      <c r="Z37" s="46" t="s">
+        <v>849</v>
+      </c>
+      <c r="AU37" s="46" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="38" spans="1:47">
+      <c r="A38" s="47" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="55" spans="1:1" ht="15">
-      <c r="A55" s="13" t="s">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1">
-      <c r="A56" s="11"/>
-    </row>
-    <row r="57" spans="1:1">
-      <c r="A57" s="11" t="s">
-        <v>1060</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1">
-      <c r="A58" s="11" t="s">
-        <v>1061</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1" ht="15">
-      <c r="A62" s="13" t="s">
-        <v>1062</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1" ht="15">
-      <c r="A64" s="13" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1">
-      <c r="A66" s="9" t="s">
-        <v>1063</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1" ht="15">
-      <c r="A68" s="13" t="s">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1">
-      <c r="A69" s="11"/>
-    </row>
-    <row r="70" spans="1:1">
-      <c r="A70" s="11" t="s">
-        <v>1064</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1">
-      <c r="A71" s="11" t="s">
-        <v>823</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1" ht="15">
-      <c r="A73" s="13" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1">
-      <c r="A75" s="29" t="s">
-        <v>824</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1">
-      <c r="A76" s="10"/>
-    </row>
-    <row r="77" spans="1:1">
-      <c r="A77" s="29" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1">
-      <c r="A78" s="29" t="s">
-        <v>826</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1">
-      <c r="A79" s="29" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1">
-      <c r="A80" s="29" t="s">
-        <v>828</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1" ht="15">
-      <c r="A82" s="13" t="s">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1">
-      <c r="A83" s="11"/>
-    </row>
-    <row r="84" spans="1:1">
-      <c r="A84" s="11" t="s">
-        <v>1065</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1">
-      <c r="A85" s="11" t="s">
-        <v>829</v>
-      </c>
-    </row>
-    <row r="89" spans="1:1" ht="15">
-      <c r="A89" s="13" t="s">
-        <v>1066</v>
-      </c>
-    </row>
-    <row r="91" spans="1:1" ht="15">
-      <c r="A91" s="13" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="93" spans="1:1">
-      <c r="A93" s="9" t="s">
-        <v>830</v>
-      </c>
-    </row>
-    <row r="95" spans="1:1" ht="15">
-      <c r="A95" s="13" t="s">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="96" spans="1:1">
-      <c r="A96" s="11"/>
-    </row>
-    <row r="97" spans="1:1">
-      <c r="A97" s="11" t="s">
-        <v>831</v>
-      </c>
-    </row>
-    <row r="98" spans="1:1">
-      <c r="A98" s="11" t="s">
-        <v>1067</v>
-      </c>
-    </row>
-    <row r="99" spans="1:1">
-      <c r="A99" s="11" t="s">
-        <v>832</v>
-      </c>
-    </row>
-    <row r="101" spans="1:1" ht="15">
-      <c r="A101" s="13" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="103" spans="1:1">
-      <c r="A103" s="29" t="s">
-        <v>833</v>
-      </c>
-    </row>
-    <row r="104" spans="1:1">
-      <c r="A104" s="29" t="s">
-        <v>834</v>
-      </c>
-    </row>
-    <row r="105" spans="1:1">
-      <c r="A105" s="29" t="s">
+      <c r="Z38" s="46" t="s">
+        <v>850</v>
+      </c>
+      <c r="AU38" s="46" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="39" spans="1:47">
+      <c r="A39" s="46" t="s">
         <v>835</v>
       </c>
-    </row>
-    <row r="106" spans="1:1">
-      <c r="A106" s="29" t="s">
+      <c r="Z39" s="46" t="s">
+        <v>64</v>
+      </c>
+      <c r="AU39" s="46" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="40" spans="1:47">
+      <c r="A40" s="46"/>
+      <c r="Z40" s="46"/>
+      <c r="AU40" s="46"/>
+    </row>
+    <row r="41" spans="1:47">
+      <c r="A41" s="46" t="s">
+        <v>836</v>
+      </c>
+      <c r="Z41" s="46" t="s">
+        <v>851</v>
+      </c>
+      <c r="AU41" s="46" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="42" spans="1:47">
+      <c r="A42" s="46" t="s">
+        <v>837</v>
+      </c>
+      <c r="Z42" s="46" t="s">
+        <v>840</v>
+      </c>
+      <c r="AU42" s="46" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="43" spans="1:47">
+      <c r="A43" s="46" t="s">
+        <v>838</v>
+      </c>
+      <c r="Z43" s="46" t="s">
+        <v>852</v>
+      </c>
+      <c r="AU43" s="46" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="44" spans="1:47">
+      <c r="A44" s="46"/>
+      <c r="Z44" s="46" t="s">
+        <v>538</v>
+      </c>
+      <c r="AU44" s="46" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="45" spans="1:47">
+      <c r="A45" s="46" t="s">
+        <v>839</v>
+      </c>
+      <c r="Z45" s="46" t="s">
+        <v>539</v>
+      </c>
+      <c r="AU45" s="46" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="46" spans="1:47">
+      <c r="A46" s="46" t="s">
+        <v>840</v>
+      </c>
+      <c r="Z46" s="46" t="s">
+        <v>540</v>
+      </c>
+      <c r="AU46" s="46" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="47" spans="1:47">
+      <c r="A47" s="46" t="s">
+        <v>841</v>
+      </c>
+      <c r="Z47" s="46" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="107" spans="1:1">
-      <c r="A107" s="29" t="s">
-        <v>836</v>
-      </c>
-    </row>
-    <row r="108" spans="1:1">
-      <c r="A108" s="10"/>
-    </row>
-    <row r="109" spans="1:1">
-      <c r="A109" s="29" t="s">
-        <v>837</v>
-      </c>
-    </row>
-    <row r="110" spans="1:1">
-      <c r="A110" s="29" t="s">
-        <v>838</v>
-      </c>
-    </row>
-    <row r="111" spans="1:1">
-      <c r="A111" s="29" t="s">
-        <v>839</v>
-      </c>
-    </row>
-    <row r="112" spans="1:1">
-      <c r="A112" s="10"/>
-    </row>
-    <row r="113" spans="1:1">
-      <c r="A113" s="29" t="s">
+      <c r="AU47" s="46"/>
+    </row>
+    <row r="48" spans="1:47">
+      <c r="A48" s="46" t="s">
+        <v>307</v>
+      </c>
+      <c r="AU48" s="46" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="49" spans="1:47" ht="15">
+      <c r="A49" s="46" t="s">
+        <v>308</v>
+      </c>
+      <c r="Z49" s="42" t="s">
+        <v>809</v>
+      </c>
+      <c r="AU49" s="46" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="50" spans="1:47">
+      <c r="A50" s="46" t="s">
+        <v>286</v>
+      </c>
+      <c r="Z50" s="45" t="s">
+        <v>1141</v>
+      </c>
+      <c r="AU50" s="46" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="51" spans="1:47">
+      <c r="A51" s="46" t="s">
+        <v>842</v>
+      </c>
+      <c r="Z51" s="45" t="s">
+        <v>1142</v>
+      </c>
+    </row>
+    <row r="52" spans="1:47" ht="15">
+      <c r="A52" s="46" t="s">
+        <v>129</v>
+      </c>
+      <c r="AU52" s="42" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="53" spans="1:47">
+      <c r="A53" s="46" t="s">
+        <v>44</v>
+      </c>
+      <c r="AU53" s="45" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="54" spans="1:47">
+      <c r="AU54" s="45" t="s">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="55" spans="1:47" ht="15">
+      <c r="A55" s="42" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="56" spans="1:47">
+      <c r="A56" s="45" t="s">
+        <v>1144</v>
+      </c>
+    </row>
+    <row r="57" spans="1:47">
+      <c r="A57" s="45" t="s">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="58" spans="1:47">
+      <c r="A58" s="45" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="59" spans="1:47" ht="15" thickBot="1"/>
+    <row r="60" spans="1:47" s="40" customFormat="1" ht="15.75" thickBot="1">
+      <c r="A60" s="39" t="s">
+        <v>1146</v>
+      </c>
+      <c r="W60" s="41" t="s">
+        <v>1147</v>
+      </c>
+      <c r="AO60" s="41" t="s">
+        <v>1148</v>
+      </c>
+    </row>
+    <row r="61" spans="1:47" ht="15">
+      <c r="A61" s="42" t="s">
+        <v>797</v>
+      </c>
+      <c r="W61" s="42" t="s">
+        <v>797</v>
+      </c>
+      <c r="AO61" s="42" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="62" spans="1:47">
+      <c r="A62" s="44" t="s">
+        <v>866</v>
+      </c>
+      <c r="W62" s="44" t="s">
+        <v>1149</v>
+      </c>
+      <c r="AO62" s="48" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="63" spans="1:47">
+      <c r="AO63" s="48" t="s">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="64" spans="1:47" ht="15">
+      <c r="A64" s="42" t="s">
+        <v>799</v>
+      </c>
+      <c r="W64" s="42" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="65" spans="1:41" ht="15">
+      <c r="A65" s="45" t="s">
+        <v>867</v>
+      </c>
+      <c r="W65" s="45" t="s">
+        <v>877</v>
+      </c>
+      <c r="AO65" s="42" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="66" spans="1:41">
+      <c r="A66" s="45" t="s">
+        <v>868</v>
+      </c>
+      <c r="W66" s="45" t="s">
+        <v>878</v>
+      </c>
+      <c r="AO66" s="45" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="67" spans="1:41">
+      <c r="A67" s="45" t="s">
+        <v>869</v>
+      </c>
+      <c r="W67" s="45" t="s">
+        <v>879</v>
+      </c>
+      <c r="AO67" s="45" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="68" spans="1:41">
+      <c r="AO68" s="45" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="69" spans="1:41" ht="15">
+      <c r="A69" s="42" t="s">
+        <v>802</v>
+      </c>
+      <c r="W69" s="42" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="70" spans="1:41" ht="15">
+      <c r="A70" s="46" t="s">
+        <v>870</v>
+      </c>
+      <c r="W70" s="47" t="s">
+        <v>880</v>
+      </c>
+      <c r="AO70" s="42" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="71" spans="1:41">
+      <c r="A71" s="46" t="s">
+        <v>871</v>
+      </c>
+      <c r="W71" s="47" t="s">
+        <v>881</v>
+      </c>
+      <c r="AO71" s="46" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="72" spans="1:41">
+      <c r="A72" s="46"/>
+      <c r="W72" s="46"/>
+      <c r="AO72" s="46" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="73" spans="1:41">
+      <c r="A73" s="46" t="s">
+        <v>872</v>
+      </c>
+      <c r="W73" s="46" t="s">
+        <v>882</v>
+      </c>
+      <c r="AO73" s="47" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="74" spans="1:41">
+      <c r="A74" s="46" t="s">
         <v>840</v>
       </c>
-    </row>
-    <row r="114" spans="1:1">
-      <c r="A114" s="29" t="s">
-        <v>841</v>
-      </c>
-    </row>
-    <row r="115" spans="1:1">
-      <c r="A115" s="29" t="s">
-        <v>842</v>
-      </c>
-    </row>
-    <row r="116" spans="1:1">
-      <c r="A116" s="29" t="s">
+      <c r="W74" s="46" t="s">
+        <v>840</v>
+      </c>
+      <c r="AO74" s="47" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="75" spans="1:41">
+      <c r="A75" s="46" t="s">
+        <v>216</v>
+      </c>
+      <c r="W75" s="46" t="s">
+        <v>883</v>
+      </c>
+      <c r="AO75" s="46" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="76" spans="1:41">
+      <c r="A76" s="46" t="s">
+        <v>873</v>
+      </c>
+      <c r="W76" s="46" t="s">
+        <v>884</v>
+      </c>
+      <c r="AO76" s="46" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="77" spans="1:41">
+      <c r="A77" s="46" t="s">
+        <v>874</v>
+      </c>
+      <c r="W77" s="46"/>
+      <c r="AO77" s="46" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="78" spans="1:41">
+      <c r="A78" s="46" t="s">
+        <v>64</v>
+      </c>
+      <c r="W78" s="46" t="s">
+        <v>885</v>
+      </c>
+      <c r="AO78" s="46" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="79" spans="1:41">
+      <c r="A79" s="46"/>
+      <c r="W79" s="46" t="s">
+        <v>886</v>
+      </c>
+      <c r="AO79" s="46" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="80" spans="1:41">
+      <c r="A80" s="46" t="s">
+        <v>875</v>
+      </c>
+      <c r="AO80" s="46"/>
+    </row>
+    <row r="81" spans="1:44" ht="15">
+      <c r="A81" s="46" t="s">
+        <v>876</v>
+      </c>
+      <c r="W81" s="42" t="s">
+        <v>809</v>
+      </c>
+      <c r="AO81" s="46" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="82" spans="1:44">
+      <c r="W82" s="45" t="s">
+        <v>1152</v>
+      </c>
+      <c r="AO82" s="46" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="83" spans="1:44" ht="15">
+      <c r="A83" s="42" t="s">
+        <v>809</v>
+      </c>
+      <c r="W83" s="45" t="s">
+        <v>1153</v>
+      </c>
+      <c r="AO83" s="46" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="84" spans="1:44">
+      <c r="A84" s="45" t="s">
+        <v>1154</v>
+      </c>
+      <c r="AO84" s="46" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="85" spans="1:44">
+      <c r="A85" s="45" t="s">
+        <v>1155</v>
+      </c>
+      <c r="AO85" s="46" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="86" spans="1:44">
+      <c r="AO86" s="46" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="87" spans="1:44">
+      <c r="AO87" s="46" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="89" spans="1:44" ht="15">
+      <c r="AO89" s="42" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="90" spans="1:44">
+      <c r="AO90" s="45" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="91" spans="1:44">
+      <c r="AO91" s="45" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="92" spans="1:44" ht="15" thickBot="1"/>
+    <row r="93" spans="1:44" s="40" customFormat="1" ht="15.75" thickBot="1">
+      <c r="A93" s="39" t="s">
+        <v>1156</v>
+      </c>
+      <c r="X93" s="41" t="s">
+        <v>1157</v>
+      </c>
+      <c r="AR93" s="41" t="s">
+        <v>1158</v>
+      </c>
+    </row>
+    <row r="94" spans="1:44" ht="15">
+      <c r="A94" s="42" t="s">
+        <v>797</v>
+      </c>
+      <c r="X94" s="42" t="s">
+        <v>797</v>
+      </c>
+      <c r="AR94" s="42" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="95" spans="1:44">
+      <c r="A95" s="44" t="s">
+        <v>1159</v>
+      </c>
+      <c r="X95" s="44" t="s">
+        <v>912</v>
+      </c>
+      <c r="AR95" s="44" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="96" spans="1:44">
+      <c r="A96" s="44" t="s">
+        <v>1118</v>
+      </c>
+    </row>
+    <row r="97" spans="1:45" ht="15">
+      <c r="A97" s="42" t="s">
+        <v>903</v>
+      </c>
+      <c r="X97" s="42" t="s">
+        <v>799</v>
+      </c>
+      <c r="AR97" s="42" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="98" spans="1:45">
+      <c r="A98" s="45" t="s">
+        <v>1119</v>
+      </c>
+      <c r="X98" s="45" t="s">
+        <v>913</v>
+      </c>
+      <c r="AR98" s="45" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="99" spans="1:45" ht="15">
+      <c r="A99" s="45" t="s">
+        <v>1120</v>
+      </c>
+      <c r="X99" s="45" t="s">
+        <v>914</v>
+      </c>
+      <c r="AR99" s="49" t="s">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="100" spans="1:45">
+      <c r="AR100" s="45" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="101" spans="1:45" ht="15">
+      <c r="A101" s="42" t="s">
+        <v>802</v>
+      </c>
+      <c r="X101" s="42" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="102" spans="1:45" ht="15">
+      <c r="A102" s="46" t="s">
+        <v>221</v>
+      </c>
+      <c r="X102" s="46" t="s">
+        <v>915</v>
+      </c>
+      <c r="AR102" s="42" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="103" spans="1:45">
+      <c r="A103" s="46" t="s">
+        <v>62</v>
+      </c>
+      <c r="X103" s="46" t="s">
+        <v>916</v>
+      </c>
+      <c r="AR103" s="46" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="104" spans="1:45">
+      <c r="A104" s="46" t="s">
+        <v>904</v>
+      </c>
+      <c r="X104" s="46" t="s">
+        <v>917</v>
+      </c>
+      <c r="AR104" s="46" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="105" spans="1:45" ht="15">
+      <c r="A105" s="46" t="s">
+        <v>905</v>
+      </c>
+      <c r="X105" s="46"/>
+      <c r="AR105" s="23" t="s">
+        <v>284</v>
+      </c>
+      <c r="AS105" s="25"/>
+    </row>
+    <row r="106" spans="1:45" ht="15">
+      <c r="A106" s="46" t="s">
+        <v>129</v>
+      </c>
+      <c r="X106" s="46" t="s">
+        <v>918</v>
+      </c>
+      <c r="AR106" s="23" t="s">
+        <v>939</v>
+      </c>
+      <c r="AS106" s="25"/>
+    </row>
+    <row r="107" spans="1:45">
+      <c r="A107" s="46" t="s">
+        <v>405</v>
+      </c>
+      <c r="X107" s="46" t="s">
+        <v>919</v>
+      </c>
+      <c r="AR107" s="46" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="108" spans="1:45">
+      <c r="A108" s="46" t="s">
+        <v>906</v>
+      </c>
+      <c r="X108" s="46" t="s">
+        <v>920</v>
+      </c>
+      <c r="AR108" s="46" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="109" spans="1:45">
+      <c r="A109" s="46" t="s">
+        <v>64</v>
+      </c>
+      <c r="X109" s="46" t="s">
+        <v>921</v>
+      </c>
+      <c r="AR109" s="46" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="110" spans="1:45">
+      <c r="A110" s="46"/>
+      <c r="X110" s="46" t="s">
+        <v>922</v>
+      </c>
+      <c r="AR110" s="46" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="111" spans="1:45">
+      <c r="A111" s="46" t="s">
+        <v>907</v>
+      </c>
+      <c r="X111" s="46" t="s">
+        <v>44</v>
+      </c>
+      <c r="AR111" s="46"/>
+    </row>
+    <row r="112" spans="1:45">
+      <c r="A112" s="46" t="s">
+        <v>908</v>
+      </c>
+      <c r="X112" s="46"/>
+      <c r="AR112" s="46" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="113" spans="1:44">
+      <c r="A113" s="46" t="s">
+        <v>909</v>
+      </c>
+      <c r="X113" s="46" t="s">
+        <v>923</v>
+      </c>
+      <c r="AR113" s="46" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="114" spans="1:44">
+      <c r="A114" s="46" t="s">
+        <v>1121</v>
+      </c>
+      <c r="X114" s="46" t="s">
+        <v>924</v>
+      </c>
+      <c r="AR114" s="46" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="115" spans="1:44">
+      <c r="X115" s="46" t="s">
+        <v>925</v>
+      </c>
+      <c r="AR115" s="46" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="117" spans="1:1">
-      <c r="A117" s="29" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="118" spans="1:1">
-      <c r="A118" s="29" t="s">
+    <row r="116" spans="1:44">
+      <c r="A116" s="43" t="s">
+        <v>1122</v>
+      </c>
+      <c r="X116" s="46" t="s">
+        <v>926</v>
+      </c>
+      <c r="AR116" s="46" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="117" spans="1:44">
+      <c r="A117" s="43" t="s">
+        <v>62</v>
+      </c>
+      <c r="X117" s="46" t="s">
+        <v>927</v>
+      </c>
+      <c r="AR117" s="46" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="118" spans="1:44" ht="15">
+      <c r="A118" s="44" t="s">
+        <v>1125</v>
+      </c>
+      <c r="X118" s="46" t="s">
+        <v>928</v>
+      </c>
+      <c r="AR118" s="46" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="119" spans="1:44">
+      <c r="A119" s="43" t="s">
+        <v>64</v>
+      </c>
+      <c r="X119" s="46" t="s">
+        <v>929</v>
+      </c>
+      <c r="AR119" s="46" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="119" spans="1:1">
-      <c r="A119" s="29" t="s">
-        <v>843</v>
-      </c>
-    </row>
-    <row r="120" spans="1:1">
-      <c r="A120" s="29" t="s">
+    <row r="120" spans="1:44">
+      <c r="A120" s="44" t="s">
+        <v>1123</v>
+      </c>
+      <c r="X120" s="46" t="s">
+        <v>930</v>
+      </c>
+      <c r="AR120" s="46" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="121" spans="1:44">
+      <c r="A121" s="44" t="s">
+        <v>1124</v>
+      </c>
+      <c r="X121" s="46" t="s">
+        <v>44</v>
+      </c>
+      <c r="AR121" s="46" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="121" spans="1:1">
-      <c r="A121" s="29" t="s">
+    <row r="122" spans="1:44">
+      <c r="X122" s="46"/>
+      <c r="AR122" s="46" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="123" spans="1:1" ht="15">
-      <c r="A123" s="13" t="s">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="124" spans="1:1">
-      <c r="A124" s="11"/>
-    </row>
-    <row r="125" spans="1:1">
-      <c r="A125" s="11" t="s">
-        <v>1068</v>
-      </c>
-    </row>
-    <row r="126" spans="1:1">
-      <c r="A126" s="30" t="s">
-        <v>1069</v>
-      </c>
-    </row>
-    <row r="127" spans="1:1">
-      <c r="A127" s="11" t="s">
-        <v>844</v>
-      </c>
-    </row>
-    <row r="131" spans="1:1" ht="15">
-      <c r="A131" s="13" t="s">
-        <v>1070</v>
-      </c>
-    </row>
-    <row r="133" spans="1:1" ht="15">
-      <c r="A133" s="13" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="135" spans="1:1">
-      <c r="A135" s="9" t="s">
-        <v>845</v>
-      </c>
-    </row>
-    <row r="137" spans="1:1" ht="15">
-      <c r="A137" s="13" t="s">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="138" spans="1:1">
-      <c r="A138" s="11"/>
-    </row>
-    <row r="139" spans="1:1">
-      <c r="A139" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="140" spans="1:1">
-      <c r="A140" s="11" t="s">
-        <v>847</v>
-      </c>
-    </row>
-    <row r="141" spans="1:1">
-      <c r="A141" s="11" t="s">
-        <v>848</v>
-      </c>
-    </row>
-    <row r="143" spans="1:1" ht="15">
-      <c r="A143" s="13" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="145" spans="1:1">
-      <c r="A145" s="29" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="146" spans="1:1">
-      <c r="A146" s="29" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="147" spans="1:1">
-      <c r="A147" s="29" t="s">
-        <v>850</v>
-      </c>
-    </row>
-    <row r="148" spans="1:1">
-      <c r="A148" s="29" t="s">
-        <v>851</v>
-      </c>
-    </row>
-    <row r="149" spans="1:1">
-      <c r="A149" s="29" t="s">
+    <row r="123" spans="1:44" ht="15">
+      <c r="A123" s="42" t="s">
+        <v>809</v>
+      </c>
+      <c r="X123" s="46" t="s">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="124" spans="1:44" ht="15">
+      <c r="A124" s="45" t="s">
+        <v>910</v>
+      </c>
+      <c r="X124" s="46" t="s">
+        <v>932</v>
+      </c>
+      <c r="AR124" s="42" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="125" spans="1:44">
+      <c r="A125" s="45" t="s">
+        <v>911</v>
+      </c>
+      <c r="X125" s="46" t="s">
+        <v>933</v>
+      </c>
+      <c r="AR125" s="45" t="s">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="126" spans="1:44">
+      <c r="AR126" s="45" t="s">
+        <v>1161</v>
+      </c>
+    </row>
+    <row r="127" spans="1:44" ht="15">
+      <c r="X127" s="42" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="128" spans="1:44">
+      <c r="X128" s="45" t="s">
+        <v>1162</v>
+      </c>
+    </row>
+    <row r="129" spans="1:64">
+      <c r="X129" s="45" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="130" spans="1:64" ht="15" thickBot="1"/>
+    <row r="131" spans="1:64" s="40" customFormat="1" ht="15.75" thickBot="1">
+      <c r="A131" s="39" t="s">
+        <v>1163</v>
+      </c>
+      <c r="V131" s="41" t="s">
+        <v>1164</v>
+      </c>
+      <c r="AT131" s="50" t="s">
+        <v>1177</v>
+      </c>
+    </row>
+    <row r="132" spans="1:64" ht="15">
+      <c r="A132" s="42" t="s">
+        <v>797</v>
+      </c>
+      <c r="V132" s="42" t="s">
+        <v>797</v>
+      </c>
+      <c r="AT132" s="26" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="133" spans="1:64" ht="15">
+      <c r="A133" s="43" t="s">
+        <v>947</v>
+      </c>
+      <c r="W133" s="44" t="s">
+        <v>1234</v>
+      </c>
+      <c r="AT133" s="44"/>
+      <c r="AU133" s="25" t="s">
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="134" spans="1:64" ht="15">
+      <c r="W134" s="44" t="s">
+        <v>1235</v>
+      </c>
+      <c r="AT134" s="44"/>
+      <c r="AU134" s="44" t="s">
+        <v>1178</v>
+      </c>
+    </row>
+    <row r="135" spans="1:64" ht="15">
+      <c r="A135" s="42" t="s">
+        <v>799</v>
+      </c>
+      <c r="W135" s="44" t="s">
+        <v>1176</v>
+      </c>
+      <c r="AT135" s="44"/>
+      <c r="AU135" s="44" t="s">
+        <v>1179</v>
+      </c>
+    </row>
+    <row r="136" spans="1:64">
+      <c r="A136" s="45" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="137" spans="1:64" ht="15">
+      <c r="A137" s="45" t="s">
+        <v>949</v>
+      </c>
+      <c r="V137" s="42" t="s">
+        <v>799</v>
+      </c>
+      <c r="AT137" s="25" t="s">
+        <v>1215</v>
+      </c>
+      <c r="BL137" s="25" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="138" spans="1:64" ht="15">
+      <c r="V138" s="45" t="s">
+        <v>961</v>
+      </c>
+      <c r="AT138" s="42" t="s">
+        <v>802</v>
+      </c>
+      <c r="BL138" s="42" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="139" spans="1:64" ht="15">
+      <c r="A139" s="42" t="s">
+        <v>802</v>
+      </c>
+      <c r="V139" s="45" t="s">
+        <v>962</v>
+      </c>
+      <c r="AT139" s="43" t="s">
+        <v>1189</v>
+      </c>
+      <c r="BL139" s="43" t="s">
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="140" spans="1:64" ht="15">
+      <c r="A140" s="46" t="s">
+        <v>950</v>
+      </c>
+      <c r="AT140" s="43" t="s">
+        <v>1181</v>
+      </c>
+      <c r="BL140" s="25" t="s">
+        <v>1218</v>
+      </c>
+    </row>
+    <row r="141" spans="1:64" ht="15">
+      <c r="A141" s="46" t="s">
+        <v>951</v>
+      </c>
+      <c r="V141" s="42" t="s">
+        <v>802</v>
+      </c>
+      <c r="AT141" s="43" t="s">
+        <v>1182</v>
+      </c>
+      <c r="BL141" s="25" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="142" spans="1:64">
+      <c r="A142" s="46" t="s">
+        <v>952</v>
+      </c>
+      <c r="V142" s="46" t="s">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="143" spans="1:64">
+      <c r="A143" s="46" t="s">
+        <v>953</v>
+      </c>
+      <c r="V143" s="46" t="s">
+        <v>964</v>
+      </c>
+      <c r="AT143" s="43" t="s">
+        <v>1183</v>
+      </c>
+      <c r="BL143" s="43" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="144" spans="1:64">
+      <c r="A144" s="46" t="s">
+        <v>44</v>
+      </c>
+      <c r="V144" s="46" t="s">
+        <v>965</v>
+      </c>
+      <c r="AT144" s="43" t="s">
+        <v>1184</v>
+      </c>
+      <c r="BL144" s="43" t="s">
+        <v>1221</v>
+      </c>
+    </row>
+    <row r="145" spans="1:64">
+      <c r="A145" s="46"/>
+      <c r="V145" s="46"/>
+      <c r="AT145" s="43" t="s">
+        <v>1185</v>
+      </c>
+      <c r="BL145" s="43" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="146" spans="1:64">
+      <c r="A146" s="46" t="s">
+        <v>954</v>
+      </c>
+      <c r="V146" s="46" t="s">
+        <v>966</v>
+      </c>
+      <c r="BL146" s="43" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="147" spans="1:64">
+      <c r="A147" s="46" t="s">
+        <v>955</v>
+      </c>
+      <c r="V147" s="46" t="s">
+        <v>967</v>
+      </c>
+      <c r="AT147" s="43" t="s">
+        <v>1186</v>
+      </c>
+    </row>
+    <row r="148" spans="1:64">
+      <c r="A148" s="46"/>
+      <c r="V148" s="46" t="s">
+        <v>968</v>
+      </c>
+      <c r="AT148" s="43" t="s">
+        <v>1187</v>
+      </c>
+      <c r="BL148" s="43" t="s">
+        <v>1203</v>
+      </c>
+    </row>
+    <row r="149" spans="1:64">
+      <c r="A149" s="46" t="s">
+        <v>956</v>
+      </c>
+      <c r="AT149" s="43" t="s">
+        <v>1188</v>
+      </c>
+      <c r="BL149" s="44" t="s">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="150" spans="1:64" ht="15">
+      <c r="A150" s="46" t="s">
+        <v>957</v>
+      </c>
+      <c r="V150" s="42" t="s">
+        <v>809</v>
+      </c>
+      <c r="BL150" s="43" t="s">
+        <v>1223</v>
+      </c>
+    </row>
+    <row r="151" spans="1:64" ht="15">
+      <c r="A151" s="46" t="s">
+        <v>958</v>
+      </c>
+      <c r="V151" s="45" t="s">
+        <v>1167</v>
+      </c>
+      <c r="AT151" s="25" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="152" spans="1:64" ht="15">
+      <c r="A152" s="46" t="s">
+        <v>959</v>
+      </c>
+      <c r="V152" s="45" t="s">
+        <v>1168</v>
+      </c>
+      <c r="AT152" s="43" t="s">
+        <v>1204</v>
+      </c>
+      <c r="BL152" s="26" t="s">
+        <v>1228</v>
+      </c>
+    </row>
+    <row r="153" spans="1:64" ht="15">
+      <c r="AT153" s="43" t="s">
+        <v>1205</v>
+      </c>
+      <c r="BL153" s="25" t="s">
+        <v>1236</v>
+      </c>
+    </row>
+    <row r="154" spans="1:64" ht="15">
+      <c r="A154" s="42" t="s">
+        <v>809</v>
+      </c>
+      <c r="V154" s="25" t="s">
+        <v>1126</v>
+      </c>
+      <c r="W154" s="44"/>
+      <c r="X154" s="44"/>
+      <c r="Y154" s="44"/>
+      <c r="Z154" s="44"/>
+      <c r="AA154" s="44"/>
+      <c r="AT154" s="43" t="s">
+        <v>1206</v>
+      </c>
+      <c r="BL154" s="43" t="s">
+        <v>1229</v>
+      </c>
+    </row>
+    <row r="155" spans="1:64" ht="15">
+      <c r="A155" s="45" t="s">
+        <v>1169</v>
+      </c>
+      <c r="V155" s="49" t="s">
+        <v>1224</v>
+      </c>
+      <c r="AT155" s="43" t="s">
+        <v>1207</v>
+      </c>
+      <c r="BL155" s="43" t="s">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="156" spans="1:64" ht="15">
+      <c r="A156" s="45" t="s">
+        <v>960</v>
+      </c>
+      <c r="V156" s="25" t="s">
+        <v>1225</v>
+      </c>
+      <c r="BL156" s="25" t="s">
+        <v>1231</v>
+      </c>
+    </row>
+    <row r="157" spans="1:64" ht="15">
+      <c r="A157" s="45"/>
+      <c r="V157" s="25" t="s">
+        <v>1226</v>
+      </c>
+      <c r="AT157" s="25" t="s">
+        <v>1208</v>
+      </c>
+      <c r="BL157" s="43" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="158" spans="1:64" ht="15">
+      <c r="A158" s="45"/>
+      <c r="V158" s="25" t="s">
+        <v>1227</v>
+      </c>
+      <c r="AT158" s="43" t="s">
+        <v>1209</v>
+      </c>
+    </row>
+    <row r="159" spans="1:64">
+      <c r="A159" s="45"/>
+      <c r="AT159" s="44" t="s">
+        <v>1210</v>
+      </c>
+      <c r="BL159" s="43" t="s">
+        <v>1232</v>
+      </c>
+    </row>
+    <row r="160" spans="1:64">
+      <c r="A160" s="45"/>
+      <c r="V160" s="44" t="s">
+        <v>688</v>
+      </c>
+      <c r="AT160" s="44" t="s">
+        <v>1211</v>
+      </c>
+      <c r="BL160" s="43" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="161" spans="1:64">
+      <c r="A161" s="45"/>
+      <c r="V161" s="44" t="s">
+        <v>1196</v>
+      </c>
+      <c r="AT161" s="43" t="s">
+        <v>1212</v>
+      </c>
+    </row>
+    <row r="162" spans="1:64">
+      <c r="A162" s="45"/>
+      <c r="V162" s="44"/>
+      <c r="AT162" s="43" t="s">
+        <v>1213</v>
+      </c>
+      <c r="BL162" s="43" t="s">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="163" spans="1:64">
+      <c r="A163" s="45"/>
+      <c r="V163" s="44" t="s">
+        <v>1197</v>
+      </c>
+      <c r="AT163" s="43" t="s">
+        <v>1214</v>
+      </c>
+      <c r="BL163" s="43" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="164" spans="1:64" ht="15">
+      <c r="A164" s="45"/>
+      <c r="V164" s="44" t="s">
+        <v>1198</v>
+      </c>
+      <c r="AT164" s="38" t="s">
+        <v>1243</v>
+      </c>
+      <c r="BL164" s="43" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="165" spans="1:64" ht="15">
+      <c r="A165" s="45"/>
+      <c r="V165" s="44"/>
+      <c r="AT165" s="25" t="s">
+        <v>1244</v>
+      </c>
+    </row>
+    <row r="166" spans="1:64" ht="15">
+      <c r="A166" s="45"/>
+      <c r="V166" s="44" t="s">
+        <v>1199</v>
+      </c>
+      <c r="BL166" s="25" t="s">
+        <v>1237</v>
+      </c>
+    </row>
+    <row r="167" spans="1:64">
+      <c r="A167" s="45"/>
+      <c r="V167" s="44" t="s">
+        <v>1200</v>
+      </c>
+      <c r="BL167" s="43" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="168" spans="1:64">
+      <c r="A168" s="45"/>
+      <c r="V168" s="44" t="s">
+        <v>1201</v>
+      </c>
+      <c r="BL168" s="43" t="s">
+        <v>1239</v>
+      </c>
+    </row>
+    <row r="169" spans="1:64" ht="15">
+      <c r="A169" s="45"/>
+      <c r="V169" s="44"/>
+      <c r="BL169" s="43" t="s">
+        <v>1242</v>
+      </c>
+    </row>
+    <row r="170" spans="1:64">
+      <c r="A170" s="45"/>
+      <c r="V170" s="44"/>
+    </row>
+    <row r="171" spans="1:64">
+      <c r="A171" s="45"/>
+      <c r="V171" s="44"/>
+      <c r="BL171" s="43" t="s">
+        <v>1240</v>
+      </c>
+    </row>
+    <row r="172" spans="1:64">
+      <c r="A172" s="45"/>
+      <c r="V172" s="44"/>
+      <c r="BL172" s="43" t="s">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="173" spans="1:64">
+      <c r="A173" s="45"/>
+      <c r="V173" s="44"/>
+      <c r="BL173" s="43" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="174" spans="1:64" ht="15">
+      <c r="A174" s="45"/>
+      <c r="V174" s="44"/>
+      <c r="BL174" s="38" t="s">
+        <v>1243</v>
+      </c>
+    </row>
+    <row r="175" spans="1:64" ht="15.75" thickBot="1">
+      <c r="A175" s="45"/>
+      <c r="V175" s="44"/>
+      <c r="BL175" s="25" t="s">
+        <v>1244</v>
+      </c>
+    </row>
+    <row r="176" spans="1:64" s="40" customFormat="1" ht="15.75" thickBot="1">
+      <c r="A176" s="41" t="s">
+        <v>1190</v>
+      </c>
+      <c r="V176" s="41" t="s">
+        <v>1191</v>
+      </c>
+      <c r="AQ176" s="41" t="s">
+        <v>1192</v>
+      </c>
+    </row>
+    <row r="177" spans="1:43" ht="15">
+      <c r="A177" s="42" t="s">
+        <v>797</v>
+      </c>
+      <c r="V177" s="42" t="s">
+        <v>797</v>
+      </c>
+      <c r="AQ177" s="42" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="178" spans="1:43">
+      <c r="A178" s="43" t="s">
+        <v>969</v>
+      </c>
+      <c r="V178" s="43" t="s">
+        <v>976</v>
+      </c>
+      <c r="AQ178" s="43" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="180" spans="1:43" ht="15">
+      <c r="A180" s="42" t="s">
+        <v>799</v>
+      </c>
+      <c r="V180" s="42" t="s">
+        <v>799</v>
+      </c>
+      <c r="AQ180" s="42" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="181" spans="1:43">
+      <c r="A181" s="45" t="s">
+        <v>970</v>
+      </c>
+      <c r="V181" s="45" t="s">
+        <v>977</v>
+      </c>
+      <c r="AQ181" s="45" t="s">
+        <v>993</v>
+      </c>
+    </row>
+    <row r="182" spans="1:43">
+      <c r="A182" s="45" t="s">
+        <v>971</v>
+      </c>
+      <c r="V182" s="45" t="s">
+        <v>978</v>
+      </c>
+      <c r="AQ182" s="45" t="s">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="183" spans="1:43">
+      <c r="V183" s="45" t="s">
+        <v>979</v>
+      </c>
+      <c r="AQ183" s="45" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="184" spans="1:43" ht="15">
+      <c r="A184" s="42" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="185" spans="1:43" ht="15">
+      <c r="A185" s="46" t="s">
+        <v>972</v>
+      </c>
+      <c r="V185" s="42" t="s">
+        <v>802</v>
+      </c>
+      <c r="AQ185" s="42" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="186" spans="1:43">
+      <c r="A186" s="46" t="s">
+        <v>973</v>
+      </c>
+      <c r="V186" s="46" t="s">
+        <v>980</v>
+      </c>
+      <c r="AQ186" s="46" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="187" spans="1:43">
+      <c r="A187" s="46"/>
+      <c r="V187" s="46" t="s">
+        <v>840</v>
+      </c>
+      <c r="AQ187" s="46" t="s">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="188" spans="1:43">
+      <c r="A188" s="46" t="s">
+        <v>974</v>
+      </c>
+      <c r="V188" s="46" t="s">
+        <v>981</v>
+      </c>
+      <c r="AQ188" s="46" t="s">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="189" spans="1:43">
+      <c r="A189" s="46" t="s">
+        <v>975</v>
+      </c>
+      <c r="V189" s="46" t="s">
+        <v>982</v>
+      </c>
+      <c r="AQ189" s="46" t="s">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="190" spans="1:43">
+      <c r="V190" s="46" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="150" spans="1:1">
-      <c r="A150" s="10"/>
-    </row>
-    <row r="151" spans="1:1">
-      <c r="A151" s="29" t="s">
-        <v>852</v>
-      </c>
-    </row>
-    <row r="152" spans="1:1">
-      <c r="A152" s="29" t="s">
-        <v>841</v>
-      </c>
-    </row>
-    <row r="153" spans="1:1">
-      <c r="A153" s="29" t="s">
-        <v>853</v>
-      </c>
-    </row>
-    <row r="154" spans="1:1">
-      <c r="A154" s="29" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="155" spans="1:1">
-      <c r="A155" s="29" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="156" spans="1:1">
-      <c r="A156" s="29" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="157" spans="1:1">
-      <c r="A157" s="29" t="s">
+      <c r="AQ190" s="46" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="191" spans="1:43" ht="15">
+      <c r="A191" s="42" t="s">
+        <v>809</v>
+      </c>
+      <c r="V191" s="46"/>
+      <c r="AQ191" s="46" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="192" spans="1:43">
+      <c r="A192" s="45" t="s">
+        <v>1165</v>
+      </c>
+      <c r="V192" s="46" t="s">
+        <v>983</v>
+      </c>
+      <c r="AQ192" s="46" t="s">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="193" spans="1:43">
+      <c r="A193" s="45" t="s">
+        <v>1166</v>
+      </c>
+      <c r="V193" s="46" t="s">
+        <v>984</v>
+      </c>
+      <c r="AQ193" s="46" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="194" spans="1:43">
+      <c r="V194" s="46" t="s">
+        <v>985</v>
+      </c>
+      <c r="AQ194" s="46" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="195" spans="1:43">
+      <c r="V195" s="46"/>
+      <c r="AQ195" s="46" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="159" spans="1:1" ht="15">
-      <c r="A159" s="13" t="s">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="160" spans="1:1">
-      <c r="A160" s="11"/>
-    </row>
-    <row r="161" spans="1:1">
-      <c r="A161" s="11" t="s">
-        <v>1071</v>
-      </c>
-    </row>
-    <row r="162" spans="1:1">
-      <c r="A162" s="30" t="s">
-        <v>1072</v>
-      </c>
-    </row>
-    <row r="166" spans="1:1" ht="15">
-      <c r="A166" s="13" t="s">
-        <v>1073</v>
-      </c>
-    </row>
-    <row r="168" spans="1:1" ht="15">
-      <c r="A168" s="13" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="169" spans="1:1">
-      <c r="A169" s="11"/>
-    </row>
-    <row r="170" spans="1:1">
-      <c r="A170" s="30" t="s">
-        <v>1074</v>
-      </c>
-    </row>
-    <row r="171" spans="1:1">
-      <c r="A171" s="30" t="s">
-        <v>1075</v>
-      </c>
-    </row>
-    <row r="173" spans="1:1" ht="15">
-      <c r="A173" s="13" t="s">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="174" spans="1:1">
-      <c r="A174" s="11"/>
-    </row>
-    <row r="175" spans="1:1">
-      <c r="A175" s="11" t="s">
-        <v>854</v>
-      </c>
-    </row>
-    <row r="176" spans="1:1">
-      <c r="A176" s="11" t="s">
-        <v>855</v>
-      </c>
-    </row>
-    <row r="177" spans="1:1">
-      <c r="A177" s="11" t="s">
-        <v>856</v>
-      </c>
-    </row>
-    <row r="179" spans="1:1" ht="15">
-      <c r="A179" s="13" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="181" spans="1:1">
-      <c r="A181" s="29" t="s">
-        <v>857</v>
-      </c>
-    </row>
-    <row r="182" spans="1:1">
-      <c r="A182" s="29" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="183" spans="1:1">
-      <c r="A183" s="29" t="s">
-        <v>859</v>
-      </c>
-    </row>
-    <row r="184" spans="1:1">
-      <c r="A184" s="29" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="185" spans="1:1">
-      <c r="A185" s="10"/>
-    </row>
-    <row r="186" spans="1:1">
-      <c r="A186" s="29" t="s">
-        <v>860</v>
-      </c>
-    </row>
-    <row r="187" spans="1:1">
-      <c r="A187" s="29" t="s">
-        <v>861</v>
-      </c>
-    </row>
-    <row r="188" spans="1:1">
-      <c r="A188" s="29" t="s">
-        <v>862</v>
-      </c>
-    </row>
-    <row r="189" spans="1:1">
-      <c r="A189" s="29" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="190" spans="1:1">
-      <c r="A190" s="29" t="s">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="191" spans="1:1">
-      <c r="A191" s="29" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="192" spans="1:1">
-      <c r="A192" s="10"/>
-    </row>
-    <row r="193" spans="1:1">
-      <c r="A193" s="29" t="s">
-        <v>864</v>
-      </c>
-    </row>
-    <row r="194" spans="1:1">
-      <c r="A194" s="29" t="s">
-        <v>865</v>
-      </c>
-    </row>
-    <row r="195" spans="1:1">
-      <c r="A195" s="29" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="197" spans="1:1" ht="15">
-      <c r="A197" s="13" t="s">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="198" spans="1:1">
-      <c r="A198" s="11"/>
-    </row>
-    <row r="199" spans="1:1">
-      <c r="A199" s="11" t="s">
-        <v>866</v>
-      </c>
-    </row>
-    <row r="200" spans="1:1">
-      <c r="A200" s="30" t="s">
-        <v>1076</v>
-      </c>
-    </row>
-    <row r="204" spans="1:1" ht="15">
-      <c r="A204" s="13" t="s">
-        <v>1077</v>
-      </c>
-    </row>
-    <row r="206" spans="1:1" ht="15">
-      <c r="A206" s="13" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="208" spans="1:1">
-      <c r="A208" s="9" t="s">
-        <v>867</v>
-      </c>
-    </row>
-    <row r="210" spans="1:1" ht="15">
-      <c r="A210" s="13" t="s">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="211" spans="1:1">
-      <c r="A211" s="11"/>
-    </row>
-    <row r="212" spans="1:1">
-      <c r="A212" s="11" t="s">
-        <v>868</v>
-      </c>
-    </row>
-    <row r="213" spans="1:1">
-      <c r="A213" s="11" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="214" spans="1:1">
-      <c r="A214" s="11" t="s">
-        <v>870</v>
-      </c>
-    </row>
-    <row r="216" spans="1:1" ht="15">
-      <c r="A216" s="13" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="218" spans="1:1">
-      <c r="A218" s="29" t="s">
-        <v>871</v>
-      </c>
-    </row>
-    <row r="219" spans="1:1">
-      <c r="A219" s="29" t="s">
-        <v>872</v>
-      </c>
-    </row>
-    <row r="220" spans="1:1">
-      <c r="A220" s="10"/>
-    </row>
-    <row r="221" spans="1:1">
-      <c r="A221" s="29" t="s">
-        <v>873</v>
-      </c>
-    </row>
-    <row r="222" spans="1:1">
-      <c r="A222" s="29" t="s">
-        <v>841</v>
-      </c>
-    </row>
-    <row r="223" spans="1:1">
-      <c r="A223" s="29" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="224" spans="1:1">
-      <c r="A224" s="29" t="s">
-        <v>874</v>
-      </c>
-    </row>
-    <row r="225" spans="1:1">
-      <c r="A225" s="29" t="s">
-        <v>875</v>
-      </c>
-    </row>
-    <row r="226" spans="1:1">
-      <c r="A226" s="29" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="227" spans="1:1">
-      <c r="A227" s="10"/>
-    </row>
-    <row r="228" spans="1:1">
-      <c r="A228" s="29" t="s">
-        <v>876</v>
-      </c>
-    </row>
-    <row r="229" spans="1:1">
-      <c r="A229" s="29" t="s">
-        <v>877</v>
-      </c>
-    </row>
-    <row r="231" spans="1:1" ht="15">
-      <c r="A231" s="13" t="s">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="232" spans="1:1">
-      <c r="A232" s="11"/>
-    </row>
-    <row r="233" spans="1:1">
-      <c r="A233" s="11" t="s">
-        <v>1078</v>
-      </c>
-    </row>
-    <row r="234" spans="1:1">
-      <c r="A234" s="30" t="s">
-        <v>1079</v>
-      </c>
-    </row>
-    <row r="238" spans="1:1" ht="15">
-      <c r="A238" s="13" t="s">
-        <v>1080</v>
-      </c>
-    </row>
-    <row r="240" spans="1:1" ht="15">
-      <c r="A240" s="13" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="242" spans="1:1">
-      <c r="A242" s="9" t="s">
-        <v>1081</v>
-      </c>
-    </row>
-    <row r="244" spans="1:1" ht="15">
-      <c r="A244" s="13" t="s">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="245" spans="1:1">
-      <c r="A245" s="11"/>
-    </row>
-    <row r="246" spans="1:1">
-      <c r="A246" s="11" t="s">
-        <v>878</v>
-      </c>
-    </row>
-    <row r="247" spans="1:1">
-      <c r="A247" s="11" t="s">
-        <v>879</v>
-      </c>
-    </row>
-    <row r="248" spans="1:1">
-      <c r="A248" s="11" t="s">
-        <v>880</v>
-      </c>
-    </row>
-    <row r="250" spans="1:1" ht="15">
-      <c r="A250" s="13" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="252" spans="1:1">
-      <c r="A252" s="29" t="s">
-        <v>881</v>
-      </c>
-    </row>
-    <row r="253" spans="1:1">
-      <c r="A253" s="29" t="s">
-        <v>882</v>
-      </c>
-    </row>
-    <row r="254" spans="1:1">
-      <c r="A254" s="10"/>
-    </row>
-    <row r="255" spans="1:1">
-      <c r="A255" s="29" t="s">
-        <v>883</v>
-      </c>
-    </row>
-    <row r="256" spans="1:1">
-      <c r="A256" s="29" t="s">
-        <v>841</v>
-      </c>
-    </row>
-    <row r="257" spans="1:1">
-      <c r="A257" s="29" t="s">
-        <v>884</v>
-      </c>
-    </row>
-    <row r="258" spans="1:1">
-      <c r="A258" s="29" t="s">
-        <v>885</v>
-      </c>
-    </row>
-    <row r="259" spans="1:1">
-      <c r="A259" s="10"/>
-    </row>
-    <row r="260" spans="1:1">
-      <c r="A260" s="29" t="s">
-        <v>886</v>
-      </c>
-    </row>
-    <row r="261" spans="1:1">
-      <c r="A261" s="29" t="s">
-        <v>887</v>
-      </c>
-    </row>
-    <row r="263" spans="1:1" ht="15">
-      <c r="A263" s="13" t="s">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="264" spans="1:1">
-      <c r="A264" s="11"/>
-    </row>
-    <row r="265" spans="1:1">
-      <c r="A265" s="11" t="s">
-        <v>1082</v>
-      </c>
-    </row>
-    <row r="266" spans="1:1">
-      <c r="A266" s="11" t="s">
-        <v>1083</v>
-      </c>
-    </row>
-    <row r="270" spans="1:1" ht="15">
-      <c r="A270" s="13" t="s">
-        <v>1084</v>
-      </c>
-    </row>
-    <row r="272" spans="1:1" ht="15">
-      <c r="A272" s="13" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="273" spans="1:1">
-      <c r="A273" s="11"/>
-    </row>
-    <row r="274" spans="1:1">
-      <c r="A274" s="30" t="s">
-        <v>1085</v>
-      </c>
+    <row r="196" spans="1:43">
+      <c r="V196" s="46" t="s">
+        <v>986</v>
+      </c>
+      <c r="AQ196" s="46"/>
+    </row>
+    <row r="197" spans="1:43">
+      <c r="V197" s="46" t="s">
+        <v>840</v>
+      </c>
+      <c r="AQ197" s="46" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="198" spans="1:43">
+      <c r="V198" s="46" t="s">
+        <v>987</v>
+      </c>
+      <c r="AQ198" s="46" t="s">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="199" spans="1:43">
+      <c r="V199" s="46" t="s">
+        <v>988</v>
+      </c>
+      <c r="AQ199" s="46" t="s">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="200" spans="1:43">
+      <c r="V200" s="46"/>
+      <c r="AQ200" s="46" t="s">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="201" spans="1:43">
+      <c r="V201" s="46" t="s">
+        <v>989</v>
+      </c>
+      <c r="AQ201" s="46" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="202" spans="1:43">
+      <c r="V202" s="46" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="203" spans="1:43" ht="15">
+      <c r="V203" s="46" t="s">
+        <v>297</v>
+      </c>
+      <c r="AQ203" s="42" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="204" spans="1:43">
+      <c r="V204" s="46" t="s">
+        <v>44</v>
+      </c>
+      <c r="AQ204" s="45" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="205" spans="1:43">
+      <c r="AQ205" s="45" t="s">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="206" spans="1:43" ht="15">
+      <c r="V206" s="42" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="207" spans="1:43">
+      <c r="V207" s="45" t="s">
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="208" spans="1:43">
+      <c r="V208" s="45" t="s">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="209" spans="1:40" ht="15" thickBot="1"/>
+    <row r="210" spans="1:40" s="40" customFormat="1" ht="15.75" thickBot="1">
+      <c r="A210" s="41" t="s">
+        <v>1193</v>
+      </c>
+      <c r="U210" s="41" t="s">
+        <v>1194</v>
+      </c>
+      <c r="AN210" s="41" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="211" spans="1:40" ht="15">
+      <c r="A211" s="42" t="s">
+        <v>797</v>
+      </c>
+      <c r="U211" s="42" t="s">
+        <v>797</v>
+      </c>
+      <c r="AN211" s="42" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="212" spans="1:40">
+      <c r="A212" s="43" t="s">
+        <v>1170</v>
+      </c>
+      <c r="U212" s="43" t="s">
+        <v>1018</v>
+      </c>
+      <c r="AN212" s="44" t="s">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="214" spans="1:40" ht="15">
+      <c r="A214" s="42" t="s">
+        <v>799</v>
+      </c>
+      <c r="U214" s="42" t="s">
+        <v>799</v>
+      </c>
+      <c r="AN214" s="42" t="s">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="215" spans="1:40">
+      <c r="A215" s="45" t="s">
+        <v>1010</v>
+      </c>
+      <c r="U215" s="48" t="s">
+        <v>1019</v>
+      </c>
+      <c r="AN215" s="48" t="s">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="216" spans="1:40">
+      <c r="A216" s="45" t="s">
+        <v>1011</v>
+      </c>
+      <c r="U216" s="48" t="s">
+        <v>1020</v>
+      </c>
+      <c r="AN216" s="48" t="s">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="217" spans="1:40">
+      <c r="A217" s="45" t="s">
+        <v>1012</v>
+      </c>
+      <c r="U217" s="48" t="s">
+        <v>1021</v>
+      </c>
+      <c r="AN217" s="48" t="s">
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="218" spans="1:40">
+      <c r="AN218" s="44"/>
+    </row>
+    <row r="219" spans="1:40" ht="15">
+      <c r="A219" s="42" t="s">
+        <v>802</v>
+      </c>
+      <c r="U219" s="42" t="s">
+        <v>802</v>
+      </c>
+      <c r="AN219" s="42" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="220" spans="1:40">
+      <c r="A220" s="46" t="s">
+        <v>1013</v>
+      </c>
+      <c r="AN220" s="47" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="221" spans="1:40">
+      <c r="A221" s="46" t="s">
+        <v>1014</v>
+      </c>
+      <c r="U221" s="47" t="s">
+        <v>1022</v>
+      </c>
+      <c r="AN221" s="47" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="222" spans="1:40">
+      <c r="A222" s="46" t="s">
+        <v>44</v>
+      </c>
+      <c r="U222" s="47" t="s">
+        <v>1023</v>
+      </c>
+      <c r="AN222" s="47" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="223" spans="1:40">
+      <c r="A223" s="46"/>
+      <c r="U223" s="46"/>
+      <c r="AN223" s="46"/>
+    </row>
+    <row r="224" spans="1:40" ht="15">
+      <c r="A224" s="46" t="s">
+        <v>1015</v>
+      </c>
+      <c r="U224" s="23" t="s">
+        <v>1024</v>
+      </c>
+      <c r="AN224" s="47" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="225" spans="1:40">
+      <c r="A225" s="46" t="s">
+        <v>1016</v>
+      </c>
+      <c r="U225" s="46" t="s">
+        <v>56</v>
+      </c>
+      <c r="AN225" s="47" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="226" spans="1:40">
+      <c r="A226" s="46" t="s">
+        <v>1017</v>
+      </c>
+      <c r="U226" s="46" t="s">
+        <v>44</v>
+      </c>
+      <c r="AN226" s="47" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="227" spans="1:40">
+      <c r="A227" s="46" t="s">
+        <v>44</v>
+      </c>
+      <c r="U227" s="46"/>
+    </row>
+    <row r="228" spans="1:40" ht="15">
+      <c r="U228" s="46" t="s">
+        <v>1025</v>
+      </c>
+      <c r="AN228" s="42" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="229" spans="1:40" ht="15">
+      <c r="A229" s="42" t="s">
+        <v>809</v>
+      </c>
+      <c r="U229" s="23" t="s">
+        <v>1026</v>
+      </c>
+      <c r="AN229" s="45" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="230" spans="1:40" ht="15">
+      <c r="A230" s="45"/>
+      <c r="U230" s="46" t="s">
+        <v>1027</v>
+      </c>
+      <c r="AN230" s="49" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="231" spans="1:40">
+      <c r="A231" s="45" t="s">
+        <v>1171</v>
+      </c>
+      <c r="AN231" s="45" t="s">
+        <v>1174</v>
+      </c>
+    </row>
+    <row r="232" spans="1:40" ht="15">
+      <c r="A232" s="45" t="s">
+        <v>1172</v>
+      </c>
+      <c r="U232" s="42" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="233" spans="1:40">
+      <c r="U233" s="48" t="s">
+        <v>1175</v>
+      </c>
+    </row>
+    <row r="234" spans="1:40">
+      <c r="U234" s="48" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="264" spans="1:1" ht="15">
+      <c r="A264" s="42"/>
+    </row>
+    <row r="266" spans="1:1" ht="15">
+      <c r="A266" s="42"/>
+    </row>
+    <row r="267" spans="1:1">
+      <c r="A267" s="45"/>
+    </row>
+    <row r="268" spans="1:1">
+      <c r="A268" s="45"/>
+    </row>
+    <row r="269" spans="1:1">
+      <c r="A269" s="45"/>
+    </row>
+    <row r="270" spans="1:1">
+      <c r="A270" s="45"/>
+    </row>
+    <row r="271" spans="1:1">
+      <c r="A271" s="45"/>
+    </row>
+    <row r="272" spans="1:1">
+      <c r="A272" s="45"/>
+    </row>
+    <row r="274" spans="1:1" ht="15">
+      <c r="A274" s="42"/>
     </row>
     <row r="275" spans="1:1">
-      <c r="A275" s="30" t="s">
-        <v>1086</v>
-      </c>
-    </row>
-    <row r="277" spans="1:1" ht="15">
-      <c r="A277" s="13" t="s">
-        <v>800</v>
-      </c>
+      <c r="A275" s="45"/>
+    </row>
+    <row r="276" spans="1:1">
+      <c r="A276" s="45"/>
+    </row>
+    <row r="277" spans="1:1">
+      <c r="A277" s="45"/>
     </row>
     <row r="278" spans="1:1">
-      <c r="A278" s="11"/>
+      <c r="A278" s="45"/>
     </row>
     <row r="279" spans="1:1">
-      <c r="A279" s="11" t="s">
-        <v>888</v>
-      </c>
+      <c r="A279" s="45"/>
     </row>
     <row r="280" spans="1:1">
-      <c r="A280" s="11" t="s">
-        <v>889</v>
-      </c>
-    </row>
-    <row r="281" spans="1:1">
-      <c r="A281" s="11" t="s">
-        <v>890</v>
-      </c>
-    </row>
-    <row r="283" spans="1:1" ht="15">
-      <c r="A283" s="13" t="s">
-        <v>803</v>
-      </c>
+      <c r="A280" s="45"/>
+    </row>
+    <row r="282" spans="1:1" ht="15">
+      <c r="A282" s="42"/>
+    </row>
+    <row r="283" spans="1:1">
+      <c r="A283" s="45"/>
+    </row>
+    <row r="284" spans="1:1">
+      <c r="A284" s="45"/>
     </row>
     <row r="285" spans="1:1">
-      <c r="A285" s="29" t="s">
-        <v>891</v>
-      </c>
+      <c r="A285" s="45"/>
     </row>
     <row r="286" spans="1:1">
-      <c r="A286" s="29" t="s">
-        <v>62</v>
-      </c>
+      <c r="A286" s="45"/>
     </row>
     <row r="287" spans="1:1">
-      <c r="A287" s="29" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="288" spans="1:1">
-      <c r="A288" s="29" t="s">
-        <v>893</v>
-      </c>
-    </row>
-    <row r="289" spans="1:1">
-      <c r="A289" s="29" t="s">
-        <v>894</v>
-      </c>
-    </row>
-    <row r="290" spans="1:1">
-      <c r="A290" s="29" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="291" spans="1:1">
-      <c r="A291" s="29" t="s">
-        <v>895</v>
-      </c>
-    </row>
-    <row r="292" spans="1:1">
-      <c r="A292" s="29" t="s">
-        <v>896</v>
-      </c>
-    </row>
-    <row r="293" spans="1:1">
-      <c r="A293" s="29" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="294" spans="1:1">
-      <c r="A294" s="10"/>
-    </row>
-    <row r="295" spans="1:1">
-      <c r="A295" s="29" t="s">
-        <v>897</v>
-      </c>
-    </row>
-    <row r="296" spans="1:1">
-      <c r="A296" s="29" t="s">
-        <v>898</v>
-      </c>
-    </row>
-    <row r="297" spans="1:1">
-      <c r="A297" s="29" t="s">
-        <v>899</v>
-      </c>
-    </row>
-    <row r="298" spans="1:1">
-      <c r="A298" s="29" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="299" spans="1:1">
-      <c r="A299" s="29" t="s">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="300" spans="1:1">
-      <c r="A300" s="29" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="301" spans="1:1">
-      <c r="A301" s="29" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="303" spans="1:1" ht="15">
-      <c r="A303" s="13" t="s">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="304" spans="1:1">
-      <c r="A304" s="11"/>
-    </row>
-    <row r="305" spans="1:1">
-      <c r="A305" s="11" t="s">
-        <v>902</v>
-      </c>
-    </row>
-    <row r="306" spans="1:1">
-      <c r="A306" s="11" t="s">
-        <v>903</v>
-      </c>
-    </row>
-    <row r="310" spans="1:1" ht="15">
-      <c r="A310" s="13" t="s">
-        <v>1087</v>
-      </c>
-    </row>
-    <row r="312" spans="1:1" ht="15">
-      <c r="A312" s="13" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="314" spans="1:1">
-      <c r="A314" s="9" t="s">
-        <v>1088</v>
-      </c>
-    </row>
-    <row r="316" spans="1:1" ht="15">
-      <c r="A316" s="13" t="s">
-        <v>904</v>
-      </c>
-    </row>
-    <row r="317" spans="1:1">
-      <c r="A317" s="11"/>
-    </row>
-    <row r="318" spans="1:1">
-      <c r="A318" s="11" t="s">
-        <v>905</v>
-      </c>
-    </row>
-    <row r="319" spans="1:1">
-      <c r="A319" s="11" t="s">
-        <v>906</v>
-      </c>
-    </row>
-    <row r="321" spans="1:1" ht="15">
-      <c r="A321" s="13" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="323" spans="1:1">
-      <c r="A323" s="29" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="324" spans="1:1">
-      <c r="A324" s="29" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="325" spans="1:1">
-      <c r="A325" s="29" t="s">
-        <v>907</v>
-      </c>
-    </row>
-    <row r="326" spans="1:1">
-      <c r="A326" s="29" t="s">
-        <v>908</v>
-      </c>
-    </row>
-    <row r="327" spans="1:1">
-      <c r="A327" s="29" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="328" spans="1:1">
-      <c r="A328" s="29" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="329" spans="1:1">
-      <c r="A329" s="29" t="s">
-        <v>909</v>
-      </c>
-    </row>
-    <row r="330" spans="1:1">
-      <c r="A330" s="29" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="331" spans="1:1">
-      <c r="A331" s="10"/>
-    </row>
-    <row r="332" spans="1:1">
-      <c r="A332" s="29" t="s">
-        <v>910</v>
-      </c>
-    </row>
-    <row r="333" spans="1:1">
-      <c r="A333" s="29" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="334" spans="1:1">
-      <c r="A334" s="29" t="s">
-        <v>912</v>
-      </c>
-    </row>
-    <row r="336" spans="1:1" ht="15">
-      <c r="A336" s="13" t="s">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="337" spans="1:1">
-      <c r="A337" s="11"/>
-    </row>
-    <row r="338" spans="1:1">
-      <c r="A338" s="11" t="s">
-        <v>913</v>
-      </c>
-    </row>
-    <row r="339" spans="1:1">
-      <c r="A339" s="11" t="s">
-        <v>914</v>
-      </c>
-    </row>
-    <row r="343" spans="1:1" ht="15">
-      <c r="A343" s="13" t="s">
-        <v>1089</v>
-      </c>
-    </row>
-    <row r="345" spans="1:1" ht="15">
-      <c r="A345" s="13" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="347" spans="1:1">
-      <c r="A347" s="9" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="349" spans="1:1" ht="15">
-      <c r="A349" s="13" t="s">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="350" spans="1:1">
-      <c r="A350" s="11"/>
-    </row>
-    <row r="351" spans="1:1">
-      <c r="A351" s="11" t="s">
-        <v>916</v>
-      </c>
-    </row>
-    <row r="352" spans="1:1">
-      <c r="A352" s="11" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="354" spans="1:1" ht="15">
-      <c r="A354" s="13" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="356" spans="1:1">
-      <c r="A356" s="29" t="s">
-        <v>918</v>
-      </c>
-    </row>
-    <row r="357" spans="1:1">
-      <c r="A357" s="29" t="s">
-        <v>919</v>
-      </c>
-    </row>
-    <row r="358" spans="1:1">
-      <c r="A358" s="29" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="359" spans="1:1">
-      <c r="A359" s="10"/>
-    </row>
-    <row r="360" spans="1:1">
-      <c r="A360" s="29" t="s">
-        <v>921</v>
-      </c>
-    </row>
-    <row r="361" spans="1:1">
-      <c r="A361" s="29" t="s">
-        <v>922</v>
-      </c>
-    </row>
-    <row r="362" spans="1:1">
-      <c r="A362" s="29" t="s">
-        <v>923</v>
-      </c>
-    </row>
-    <row r="363" spans="1:1">
-      <c r="A363" s="29" t="s">
-        <v>924</v>
-      </c>
-    </row>
-    <row r="364" spans="1:1">
-      <c r="A364" s="29" t="s">
-        <v>925</v>
-      </c>
-    </row>
-    <row r="365" spans="1:1">
-      <c r="A365" s="29" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="366" spans="1:1">
-      <c r="A366" s="10"/>
-    </row>
-    <row r="367" spans="1:1">
-      <c r="A367" s="29" t="s">
-        <v>926</v>
-      </c>
-    </row>
-    <row r="368" spans="1:1">
-      <c r="A368" s="29" t="s">
-        <v>927</v>
-      </c>
-    </row>
-    <row r="369" spans="1:1">
-      <c r="A369" s="29" t="s">
-        <v>928</v>
-      </c>
-    </row>
-    <row r="370" spans="1:1">
-      <c r="A370" s="29" t="s">
-        <v>929</v>
-      </c>
-    </row>
-    <row r="371" spans="1:1">
-      <c r="A371" s="29" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="372" spans="1:1">
-      <c r="A372" s="29" t="s">
-        <v>931</v>
-      </c>
-    </row>
-    <row r="373" spans="1:1">
-      <c r="A373" s="29" t="s">
-        <v>932</v>
-      </c>
-    </row>
-    <row r="374" spans="1:1">
-      <c r="A374" s="29" t="s">
-        <v>933</v>
-      </c>
-    </row>
-    <row r="375" spans="1:1">
-      <c r="A375" s="29" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="376" spans="1:1">
-      <c r="A376" s="10"/>
-    </row>
-    <row r="377" spans="1:1">
-      <c r="A377" s="29" t="s">
-        <v>934</v>
-      </c>
-    </row>
-    <row r="378" spans="1:1">
-      <c r="A378" s="29" t="s">
-        <v>935</v>
-      </c>
-    </row>
-    <row r="379" spans="1:1">
-      <c r="A379" s="29" t="s">
-        <v>936</v>
-      </c>
-    </row>
-    <row r="381" spans="1:1" ht="15">
-      <c r="A381" s="13" t="s">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="382" spans="1:1">
-      <c r="A382" s="11"/>
-    </row>
-    <row r="383" spans="1:1">
-      <c r="A383" s="11" t="s">
-        <v>1090</v>
-      </c>
-    </row>
-    <row r="384" spans="1:1">
-      <c r="A384" s="11" t="s">
-        <v>937</v>
-      </c>
-    </row>
-    <row r="388" spans="1:1" ht="15">
-      <c r="A388" s="13" t="s">
-        <v>1091</v>
-      </c>
-    </row>
-    <row r="390" spans="1:1" ht="15">
-      <c r="A390" s="13" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="392" spans="1:1">
-      <c r="A392" s="9" t="s">
-        <v>938</v>
-      </c>
-    </row>
-    <row r="394" spans="1:1" ht="15">
-      <c r="A394" s="13" t="s">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="395" spans="1:1">
-      <c r="A395" s="11"/>
-    </row>
-    <row r="396" spans="1:1">
-      <c r="A396" s="11" t="s">
-        <v>939</v>
-      </c>
-    </row>
-    <row r="397" spans="1:1">
-      <c r="A397" s="11" t="s">
-        <v>940</v>
-      </c>
-    </row>
-    <row r="398" spans="1:1">
-      <c r="A398" s="11" t="s">
-        <v>941</v>
-      </c>
-    </row>
-    <row r="400" spans="1:1" ht="15">
-      <c r="A400" s="13" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="402" spans="1:1">
-      <c r="A402" s="29" t="s">
-        <v>841</v>
-      </c>
-    </row>
-    <row r="403" spans="1:1">
-      <c r="A403" s="29" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="404" spans="1:1">
-      <c r="A404" s="29" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="405" spans="1:1">
-      <c r="A405" s="29" t="s">
-        <v>942</v>
-      </c>
-    </row>
-    <row r="406" spans="1:1">
-      <c r="A406" s="29" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="407" spans="1:1">
-      <c r="A407" s="29" t="s">
-        <v>943</v>
-      </c>
-    </row>
-    <row r="408" spans="1:1">
-      <c r="A408" s="29" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="409" spans="1:1">
-      <c r="A409" s="29" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="410" spans="1:1">
-      <c r="A410" s="10"/>
-    </row>
-    <row r="411" spans="1:1">
-      <c r="A411" s="29" t="s">
-        <v>944</v>
-      </c>
-    </row>
-    <row r="412" spans="1:1">
-      <c r="A412" s="29" t="s">
-        <v>841</v>
-      </c>
-    </row>
-    <row r="413" spans="1:1">
-      <c r="A413" s="29" t="s">
-        <v>945</v>
-      </c>
-    </row>
-    <row r="414" spans="1:1">
-      <c r="A414" s="29" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="415" spans="1:1">
-      <c r="A415" s="29" t="s">
-        <v>946</v>
-      </c>
-    </row>
-    <row r="416" spans="1:1">
-      <c r="A416" s="29" t="s">
-        <v>947</v>
-      </c>
-    </row>
-    <row r="417" spans="1:1">
-      <c r="A417" s="29" t="s">
-        <v>948</v>
-      </c>
-    </row>
-    <row r="418" spans="1:1">
-      <c r="A418" s="29" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="419" spans="1:1">
-      <c r="A419" s="29" t="s">
-        <v>949</v>
-      </c>
-    </row>
-    <row r="420" spans="1:1">
-      <c r="A420" s="29" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="421" spans="1:1">
-      <c r="A421" s="29" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="423" spans="1:1" ht="15">
-      <c r="A423" s="13" t="s">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="424" spans="1:1">
-      <c r="A424" s="11"/>
-    </row>
-    <row r="425" spans="1:1">
-      <c r="A425" s="11" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="426" spans="1:1">
-      <c r="A426" s="11" t="s">
-        <v>1093</v>
-      </c>
-    </row>
-    <row r="430" spans="1:1" ht="15">
-      <c r="A430" s="13" t="s">
-        <v>1094</v>
-      </c>
-    </row>
-    <row r="432" spans="1:1" ht="15">
-      <c r="A432" s="13" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="434" spans="1:1">
-      <c r="A434" s="9" t="s">
-        <v>950</v>
-      </c>
-    </row>
-    <row r="436" spans="1:1" ht="15">
-      <c r="A436" s="13" t="s">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="437" spans="1:1">
-      <c r="A437" s="11"/>
-    </row>
-    <row r="438" spans="1:1">
-      <c r="A438" s="11" t="s">
-        <v>951</v>
-      </c>
-    </row>
-    <row r="439" spans="1:1">
-      <c r="A439" s="11" t="s">
-        <v>952</v>
-      </c>
-    </row>
-    <row r="441" spans="1:1" ht="15">
-      <c r="A441" s="13" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="443" spans="1:1">
-      <c r="A443" s="29" t="s">
-        <v>953</v>
-      </c>
-    </row>
-    <row r="444" spans="1:1">
-      <c r="A444" s="29" t="s">
-        <v>954</v>
-      </c>
-    </row>
-    <row r="445" spans="1:1">
-      <c r="A445" s="29" t="s">
-        <v>955</v>
-      </c>
-    </row>
-    <row r="446" spans="1:1">
-      <c r="A446" s="29" t="s">
-        <v>956</v>
-      </c>
-    </row>
-    <row r="447" spans="1:1">
-      <c r="A447" s="29" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="448" spans="1:1">
-      <c r="A448" s="10"/>
-    </row>
-    <row r="449" spans="1:1">
-      <c r="A449" s="29" t="s">
-        <v>957</v>
-      </c>
-    </row>
-    <row r="450" spans="1:1">
-      <c r="A450" s="29" t="s">
-        <v>958</v>
-      </c>
-    </row>
-    <row r="451" spans="1:1">
-      <c r="A451" s="10"/>
-    </row>
-    <row r="452" spans="1:1">
-      <c r="A452" s="29" t="s">
-        <v>959</v>
-      </c>
-    </row>
-    <row r="453" spans="1:1">
-      <c r="A453" s="29" t="s">
-        <v>960</v>
-      </c>
-    </row>
-    <row r="454" spans="1:1">
-      <c r="A454" s="29" t="s">
-        <v>961</v>
-      </c>
-    </row>
-    <row r="455" spans="1:1">
-      <c r="A455" s="29" t="s">
-        <v>962</v>
-      </c>
-    </row>
-    <row r="457" spans="1:1" ht="15">
-      <c r="A457" s="13" t="s">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="458" spans="1:1">
-      <c r="A458" s="11"/>
-    </row>
-    <row r="459" spans="1:1">
-      <c r="A459" s="11" t="s">
-        <v>1095</v>
-      </c>
-    </row>
-    <row r="460" spans="1:1">
-      <c r="A460" s="11" t="s">
-        <v>963</v>
-      </c>
-    </row>
-    <row r="464" spans="1:1" ht="15">
-      <c r="A464" s="13" t="s">
-        <v>1096</v>
-      </c>
-    </row>
-    <row r="466" spans="1:1" ht="15">
-      <c r="A466" s="13" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="468" spans="1:1">
-      <c r="A468" s="9" t="s">
-        <v>964</v>
-      </c>
-    </row>
-    <row r="470" spans="1:1" ht="15">
-      <c r="A470" s="13" t="s">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="471" spans="1:1">
-      <c r="A471" s="11"/>
-    </row>
-    <row r="472" spans="1:1">
-      <c r="A472" s="11" t="s">
-        <v>965</v>
-      </c>
-    </row>
-    <row r="473" spans="1:1">
-      <c r="A473" s="11" t="s">
-        <v>966</v>
-      </c>
-    </row>
-    <row r="475" spans="1:1" ht="15">
-      <c r="A475" s="13" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="477" spans="1:1">
-      <c r="A477" s="29" t="s">
-        <v>967</v>
-      </c>
-    </row>
-    <row r="478" spans="1:1">
-      <c r="A478" s="29" t="s">
-        <v>968</v>
-      </c>
-    </row>
-    <row r="479" spans="1:1">
-      <c r="A479" s="29" t="s">
-        <v>969</v>
-      </c>
-    </row>
-    <row r="480" spans="1:1">
-      <c r="A480" s="10"/>
-    </row>
-    <row r="481" spans="1:1">
-      <c r="A481" s="29" t="s">
-        <v>970</v>
-      </c>
-    </row>
-    <row r="482" spans="1:1">
-      <c r="A482" s="29" t="s">
-        <v>971</v>
-      </c>
-    </row>
-    <row r="483" spans="1:1">
-      <c r="A483" s="29" t="s">
-        <v>972</v>
-      </c>
-    </row>
-    <row r="485" spans="1:1" ht="15">
-      <c r="A485" s="13" t="s">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="486" spans="1:1">
-      <c r="A486" s="11"/>
-    </row>
-    <row r="487" spans="1:1">
-      <c r="A487" s="11" t="s">
-        <v>1097</v>
-      </c>
-    </row>
-    <row r="488" spans="1:1">
-      <c r="A488" s="11" t="s">
-        <v>1098</v>
-      </c>
-    </row>
-    <row r="492" spans="1:1" ht="15">
-      <c r="A492" s="13" t="s">
-        <v>1099</v>
-      </c>
-    </row>
-    <row r="494" spans="1:1" ht="15">
-      <c r="A494" s="13" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="496" spans="1:1">
-      <c r="A496" s="9" t="s">
-        <v>973</v>
-      </c>
-    </row>
-    <row r="498" spans="1:1" ht="15">
-      <c r="A498" s="13" t="s">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="499" spans="1:1">
-      <c r="A499" s="11"/>
-    </row>
-    <row r="500" spans="1:1">
-      <c r="A500" s="11" t="s">
-        <v>974</v>
-      </c>
-    </row>
-    <row r="501" spans="1:1">
-      <c r="A501" s="11" t="s">
-        <v>975</v>
-      </c>
-    </row>
-    <row r="503" spans="1:1" ht="15">
-      <c r="A503" s="13" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="505" spans="1:1">
-      <c r="A505" s="29" t="s">
-        <v>976</v>
-      </c>
-    </row>
-    <row r="506" spans="1:1">
-      <c r="A506" s="29" t="s">
-        <v>977</v>
-      </c>
-    </row>
-    <row r="507" spans="1:1">
-      <c r="A507" s="10"/>
-    </row>
-    <row r="508" spans="1:1">
-      <c r="A508" s="29" t="s">
-        <v>978</v>
-      </c>
-    </row>
-    <row r="509" spans="1:1">
-      <c r="A509" s="29" t="s">
-        <v>979</v>
-      </c>
-    </row>
-    <row r="511" spans="1:1" ht="15">
-      <c r="A511" s="13" t="s">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="512" spans="1:1">
-      <c r="A512" s="11"/>
-    </row>
-    <row r="513" spans="1:1">
-      <c r="A513" s="11" t="s">
-        <v>1100</v>
-      </c>
-    </row>
-    <row r="514" spans="1:1">
-      <c r="A514" s="30" t="s">
-        <v>1101</v>
-      </c>
-    </row>
-    <row r="518" spans="1:1" ht="15">
-      <c r="A518" s="13" t="s">
-        <v>1102</v>
-      </c>
-    </row>
-    <row r="520" spans="1:1" ht="15">
-      <c r="A520" s="13" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="522" spans="1:1">
-      <c r="A522" s="9" t="s">
-        <v>980</v>
-      </c>
-    </row>
-    <row r="524" spans="1:1" ht="15">
-      <c r="A524" s="13" t="s">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="525" spans="1:1">
-      <c r="A525" s="11"/>
-    </row>
-    <row r="526" spans="1:1">
-      <c r="A526" s="11" t="s">
-        <v>981</v>
-      </c>
-    </row>
-    <row r="527" spans="1:1">
-      <c r="A527" s="11" t="s">
-        <v>982</v>
-      </c>
-    </row>
-    <row r="528" spans="1:1">
-      <c r="A528" s="11" t="s">
-        <v>983</v>
-      </c>
-    </row>
-    <row r="530" spans="1:1" ht="15">
-      <c r="A530" s="13" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="532" spans="1:1">
-      <c r="A532" s="29" t="s">
-        <v>984</v>
-      </c>
-    </row>
-    <row r="533" spans="1:1">
-      <c r="A533" s="29" t="s">
-        <v>841</v>
-      </c>
-    </row>
-    <row r="534" spans="1:1">
-      <c r="A534" s="29" t="s">
-        <v>985</v>
-      </c>
-    </row>
-    <row r="535" spans="1:1">
-      <c r="A535" s="29" t="s">
-        <v>986</v>
-      </c>
-    </row>
-    <row r="536" spans="1:1">
-      <c r="A536" s="29" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="537" spans="1:1">
-      <c r="A537" s="10"/>
-    </row>
-    <row r="538" spans="1:1">
-      <c r="A538" s="29" t="s">
-        <v>987</v>
-      </c>
-    </row>
-    <row r="539" spans="1:1">
-      <c r="A539" s="29" t="s">
-        <v>988</v>
-      </c>
-    </row>
-    <row r="540" spans="1:1">
-      <c r="A540" s="29" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="541" spans="1:1">
-      <c r="A541" s="10"/>
-    </row>
-    <row r="542" spans="1:1">
-      <c r="A542" s="29" t="s">
-        <v>990</v>
-      </c>
-    </row>
-    <row r="543" spans="1:1">
-      <c r="A543" s="29" t="s">
-        <v>841</v>
-      </c>
-    </row>
-    <row r="544" spans="1:1">
-      <c r="A544" s="29" t="s">
-        <v>991</v>
-      </c>
-    </row>
-    <row r="545" spans="1:1">
-      <c r="A545" s="29" t="s">
-        <v>992</v>
-      </c>
-    </row>
-    <row r="546" spans="1:1">
-      <c r="A546" s="10"/>
-    </row>
-    <row r="547" spans="1:1">
-      <c r="A547" s="29" t="s">
-        <v>993</v>
-      </c>
-    </row>
-    <row r="548" spans="1:1">
-      <c r="A548" s="29" t="s">
-        <v>994</v>
-      </c>
-    </row>
-    <row r="549" spans="1:1">
-      <c r="A549" s="29" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="550" spans="1:1">
-      <c r="A550" s="29" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="552" spans="1:1" ht="15">
-      <c r="A552" s="13" t="s">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="553" spans="1:1">
-      <c r="A553" s="11"/>
-    </row>
-    <row r="554" spans="1:1">
-      <c r="A554" s="11" t="s">
-        <v>1103</v>
-      </c>
-    </row>
-    <row r="555" spans="1:1">
-      <c r="A555" s="11" t="s">
-        <v>995</v>
-      </c>
-    </row>
-    <row r="559" spans="1:1" ht="15">
-      <c r="A559" s="13" t="s">
-        <v>1104</v>
-      </c>
-    </row>
-    <row r="561" spans="1:1" ht="15">
-      <c r="A561" s="13" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="563" spans="1:1">
-      <c r="A563" s="9" t="s">
-        <v>996</v>
-      </c>
-    </row>
-    <row r="565" spans="1:1" ht="15">
-      <c r="A565" s="13" t="s">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="566" spans="1:1">
-      <c r="A566" s="11"/>
-    </row>
-    <row r="567" spans="1:1">
-      <c r="A567" s="11" t="s">
-        <v>997</v>
-      </c>
-    </row>
-    <row r="568" spans="1:1">
-      <c r="A568" s="11" t="s">
-        <v>998</v>
-      </c>
-    </row>
-    <row r="569" spans="1:1">
-      <c r="A569" s="11" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="571" spans="1:1" ht="15">
-      <c r="A571" s="13" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="573" spans="1:1">
-      <c r="A573" s="29" t="s">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="574" spans="1:1">
-      <c r="A574" s="29" t="s">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="575" spans="1:1">
-      <c r="A575" s="29" t="s">
-        <v>1002</v>
-      </c>
-    </row>
-    <row r="576" spans="1:1">
-      <c r="A576" s="29" t="s">
-        <v>1003</v>
-      </c>
-    </row>
-    <row r="577" spans="1:1">
-      <c r="A577" s="29" t="s">
-        <v>1004</v>
-      </c>
-    </row>
-    <row r="578" spans="1:1">
-      <c r="A578" s="29" t="s">
-        <v>1005</v>
-      </c>
-    </row>
-    <row r="579" spans="1:1">
-      <c r="A579" s="29" t="s">
-        <v>1006</v>
-      </c>
-    </row>
-    <row r="580" spans="1:1">
-      <c r="A580" s="29" t="s">
-        <v>1007</v>
-      </c>
-    </row>
-    <row r="581" spans="1:1">
-      <c r="A581" s="29" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="582" spans="1:1">
-      <c r="A582" s="29" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="583" spans="1:1">
-      <c r="A583" s="10"/>
-    </row>
-    <row r="584" spans="1:1">
-      <c r="A584" s="29" t="s">
-        <v>1008</v>
-      </c>
-    </row>
-    <row r="585" spans="1:1">
-      <c r="A585" s="29" t="s">
-        <v>1009</v>
-      </c>
-    </row>
-    <row r="586" spans="1:1">
-      <c r="A586" s="29" t="s">
-        <v>1010</v>
-      </c>
-    </row>
-    <row r="587" spans="1:1">
-      <c r="A587" s="29" t="s">
-        <v>1011</v>
-      </c>
-    </row>
-    <row r="588" spans="1:1">
-      <c r="A588" s="29" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="590" spans="1:1" ht="15">
-      <c r="A590" s="13" t="s">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="591" spans="1:1">
-      <c r="A591" s="11"/>
-    </row>
-    <row r="592" spans="1:1">
-      <c r="A592" s="11" t="s">
-        <v>1012</v>
-      </c>
-    </row>
-    <row r="593" spans="1:1">
-      <c r="A593" s="11" t="s">
-        <v>1013</v>
-      </c>
-    </row>
-    <row r="597" spans="1:1" ht="15">
-      <c r="A597" s="13" t="s">
-        <v>1105</v>
-      </c>
-    </row>
-    <row r="599" spans="1:1" ht="15">
-      <c r="A599" s="13" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="601" spans="1:1">
-      <c r="A601" s="9" t="s">
-        <v>1106</v>
-      </c>
-    </row>
-    <row r="603" spans="1:1" ht="15">
-      <c r="A603" s="13" t="s">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="604" spans="1:1">
-      <c r="A604" s="11"/>
-    </row>
-    <row r="605" spans="1:1">
-      <c r="A605" s="11" t="s">
-        <v>1014</v>
-      </c>
-    </row>
-    <row r="606" spans="1:1">
-      <c r="A606" s="11" t="s">
-        <v>1015</v>
-      </c>
-    </row>
-    <row r="607" spans="1:1">
-      <c r="A607" s="11" t="s">
-        <v>1016</v>
-      </c>
-    </row>
-    <row r="609" spans="1:1" ht="15">
-      <c r="A609" s="13" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="611" spans="1:1">
-      <c r="A611" s="29" t="s">
-        <v>1017</v>
-      </c>
-    </row>
-    <row r="612" spans="1:1">
-      <c r="A612" s="29" t="s">
-        <v>1018</v>
-      </c>
-    </row>
-    <row r="613" spans="1:1">
-      <c r="A613" s="29" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="614" spans="1:1">
-      <c r="A614" s="10"/>
-    </row>
-    <row r="615" spans="1:1">
-      <c r="A615" s="29" t="s">
-        <v>1019</v>
-      </c>
-    </row>
-    <row r="616" spans="1:1">
-      <c r="A616" s="29" t="s">
-        <v>1020</v>
-      </c>
-    </row>
-    <row r="617" spans="1:1">
-      <c r="A617" s="29" t="s">
-        <v>1021</v>
-      </c>
-    </row>
-    <row r="618" spans="1:1">
-      <c r="A618" s="29" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="620" spans="1:1" ht="15">
-      <c r="A620" s="13" t="s">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="621" spans="1:1">
-      <c r="A621" s="11"/>
-    </row>
-    <row r="622" spans="1:1">
-      <c r="A622" s="30" t="s">
-        <v>1107</v>
-      </c>
-    </row>
-    <row r="623" spans="1:1">
-      <c r="A623" s="30" t="s">
-        <v>1108</v>
-      </c>
-    </row>
-    <row r="627" spans="1:1" ht="15">
-      <c r="A627" s="13" t="s">
-        <v>1109</v>
-      </c>
-    </row>
-    <row r="629" spans="1:1" ht="15">
-      <c r="A629" s="13" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="631" spans="1:1">
-      <c r="A631" s="9" t="s">
-        <v>1022</v>
-      </c>
-    </row>
-    <row r="633" spans="1:1" ht="15">
-      <c r="A633" s="13" t="s">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="634" spans="1:1">
-      <c r="A634" s="11"/>
-    </row>
-    <row r="635" spans="1:1">
-      <c r="A635" s="11" t="s">
-        <v>1023</v>
-      </c>
-    </row>
-    <row r="636" spans="1:1">
-      <c r="A636" s="11" t="s">
-        <v>1024</v>
-      </c>
-    </row>
-    <row r="637" spans="1:1">
-      <c r="A637" s="11" t="s">
-        <v>1025</v>
-      </c>
-    </row>
-    <row r="639" spans="1:1" ht="15">
-      <c r="A639" s="13" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="641" spans="1:1">
-      <c r="A641" s="29" t="s">
-        <v>1026</v>
-      </c>
-    </row>
-    <row r="642" spans="1:1">
-      <c r="A642" s="29" t="s">
-        <v>1027</v>
-      </c>
-    </row>
-    <row r="643" spans="1:1">
-      <c r="A643" s="10"/>
-    </row>
-    <row r="644" spans="1:1">
-      <c r="A644" s="29" t="s">
-        <v>1028</v>
-      </c>
-    </row>
-    <row r="645" spans="1:1">
-      <c r="A645" s="29" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="646" spans="1:1">
-      <c r="A646" s="29" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="647" spans="1:1">
-      <c r="A647" s="10"/>
-    </row>
-    <row r="648" spans="1:1">
-      <c r="A648" s="29" t="s">
-        <v>1029</v>
-      </c>
-    </row>
-    <row r="649" spans="1:1">
-      <c r="A649" s="29" t="s">
-        <v>1030</v>
-      </c>
-    </row>
-    <row r="650" spans="1:1">
-      <c r="A650" s="29" t="s">
-        <v>1031</v>
-      </c>
-    </row>
-    <row r="652" spans="1:1" ht="15">
-      <c r="A652" s="13" t="s">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="653" spans="1:1">
-      <c r="A653" s="11"/>
-    </row>
-    <row r="654" spans="1:1">
-      <c r="A654" s="11" t="s">
-        <v>1110</v>
-      </c>
-    </row>
-    <row r="655" spans="1:1">
-      <c r="A655" s="11" t="s">
-        <v>1032</v>
-      </c>
-    </row>
-    <row r="659" spans="1:1" ht="15">
-      <c r="A659" s="13" t="s">
-        <v>1111</v>
-      </c>
-    </row>
-    <row r="661" spans="1:1" ht="15">
-      <c r="A661" s="13" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="663" spans="1:1">
-      <c r="A663" s="9" t="s">
-        <v>1033</v>
-      </c>
-    </row>
-    <row r="665" spans="1:1" ht="15">
-      <c r="A665" s="13" t="s">
-        <v>1034</v>
-      </c>
-    </row>
-    <row r="666" spans="1:1">
-      <c r="A666" s="11"/>
-    </row>
-    <row r="667" spans="1:1">
-      <c r="A667" s="11" t="s">
-        <v>1035</v>
-      </c>
-    </row>
-    <row r="668" spans="1:1">
-      <c r="A668" s="11" t="s">
-        <v>1036</v>
-      </c>
-    </row>
-    <row r="669" spans="1:1">
-      <c r="A669" s="11" t="s">
-        <v>1037</v>
-      </c>
-    </row>
-    <row r="671" spans="1:1" ht="15">
-      <c r="A671" s="13" t="s">
-        <v>1038</v>
-      </c>
-    </row>
-    <row r="673" spans="1:1">
-      <c r="A673" s="29" t="s">
-        <v>1039</v>
-      </c>
-    </row>
-    <row r="674" spans="1:1">
-      <c r="A674" s="29" t="s">
-        <v>1040</v>
-      </c>
-    </row>
-    <row r="675" spans="1:1">
-      <c r="A675" s="29" t="s">
-        <v>1041</v>
-      </c>
-    </row>
-    <row r="676" spans="1:1">
-      <c r="A676" s="10"/>
-    </row>
-    <row r="677" spans="1:1">
-      <c r="A677" s="29" t="s">
-        <v>1042</v>
-      </c>
-    </row>
-    <row r="678" spans="1:1">
-      <c r="A678" s="29" t="s">
-        <v>1043</v>
-      </c>
-    </row>
-    <row r="679" spans="1:1">
-      <c r="A679" s="29" t="s">
-        <v>1044</v>
-      </c>
-    </row>
-    <row r="681" spans="1:1" ht="15">
-      <c r="A681" s="13" t="s">
-        <v>1045</v>
-      </c>
-    </row>
-    <row r="682" spans="1:1">
-      <c r="A682" s="11"/>
-    </row>
-    <row r="683" spans="1:1">
-      <c r="A683" s="11" t="s">
-        <v>1046</v>
-      </c>
-    </row>
-    <row r="684" spans="1:1" ht="15">
-      <c r="A684" s="8" t="s">
-        <v>1047</v>
-      </c>
-    </row>
-    <row r="685" spans="1:1">
-      <c r="A685" s="11" t="s">
-        <v>1112</v>
-      </c>
-    </row>
-    <row r="689" spans="1:1" ht="15">
-      <c r="A689" s="13" t="s">
-        <v>1048</v>
-      </c>
-    </row>
-    <row r="691" spans="1:1" ht="15">
-      <c r="A691" s="13" t="s">
-        <v>1049</v>
-      </c>
-    </row>
-    <row r="692" spans="1:1">
-      <c r="A692" s="11"/>
-    </row>
-    <row r="693" spans="1:1">
-      <c r="A693" s="30" t="s">
-        <v>1113</v>
-      </c>
-    </row>
-    <row r="694" spans="1:1">
-      <c r="A694" s="30" t="s">
-        <v>1114</v>
-      </c>
-    </row>
-    <row r="695" spans="1:1">
-      <c r="A695" s="30" t="s">
-        <v>1115</v>
-      </c>
-    </row>
-    <row r="696" spans="1:1">
-      <c r="A696" s="30" t="s">
-        <v>1116</v>
-      </c>
-    </row>
-    <row r="697" spans="1:1">
-      <c r="A697" s="30" t="s">
-        <v>1117</v>
-      </c>
-    </row>
-    <row r="699" spans="1:1" ht="15">
-      <c r="A699" s="13" t="s">
-        <v>1050</v>
-      </c>
-    </row>
-    <row r="700" spans="1:1">
-      <c r="A700" s="11"/>
-    </row>
-    <row r="701" spans="1:1">
-      <c r="A701" s="11" t="s">
-        <v>1051</v>
-      </c>
-    </row>
-    <row r="702" spans="1:1">
-      <c r="A702" s="30" t="s">
-        <v>1118</v>
-      </c>
-    </row>
-    <row r="703" spans="1:1">
-      <c r="A703" s="30" t="s">
-        <v>1052</v>
-      </c>
-    </row>
-    <row r="704" spans="1:1">
-      <c r="A704" s="30" t="s">
-        <v>1053</v>
-      </c>
-    </row>
-    <row r="705" spans="1:1">
-      <c r="A705" s="30" t="s">
-        <v>1119</v>
-      </c>
-    </row>
-    <row r="707" spans="1:1" ht="15">
-      <c r="A707" s="13" t="s">
-        <v>1054</v>
-      </c>
-    </row>
-    <row r="708" spans="1:1">
-      <c r="A708" s="11"/>
-    </row>
-    <row r="709" spans="1:1">
-      <c r="A709" s="11" t="s">
-        <v>1055</v>
-      </c>
-    </row>
-    <row r="710" spans="1:1">
-      <c r="A710" s="11" t="s">
-        <v>1056</v>
-      </c>
-    </row>
-    <row r="711" spans="1:1">
-      <c r="A711" s="11" t="s">
-        <v>1057</v>
-      </c>
-    </row>
-    <row r="712" spans="1:1">
-      <c r="A712" s="30" t="s">
-        <v>1120</v>
-      </c>
+      <c r="A287" s="45"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
